--- a/seesauna-attersee/Rechenmodell_Seesauna_Attersee.xlsx
+++ b/seesauna-attersee/Rechenmodell_Seesauna_Attersee.xlsx
@@ -14,8 +14,9 @@
     <sheet name="Investition" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Umsatz" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Betriebskosten" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="GuV_10J" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="Gemeinden" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Stellenplan" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="GuV_10J" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Gemeinden" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="379">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="443">
   <si>
     <t xml:space="preserve">Szenarienvergleich – Normaljahr</t>
   </si>
@@ -338,7 +339,7 @@
     <t xml:space="preserve">VZÄ</t>
   </si>
   <si>
-    <t xml:space="preserve">Kassa 4, Saunameister:innen 5, Reinigung 4, Gastro 5, Leitung/Technik 2</t>
+    <t xml:space="preserve">Basis = Blatt Stellenplan; pessimistisch +1 VZÄ</t>
   </si>
   <si>
     <t xml:space="preserve">k_fte</t>
@@ -347,7 +348,7 @@
     <t xml:space="preserve">Personalkosten je VZÄ (inkl. Lohnnebenkosten)</t>
   </si>
   <si>
-    <t xml:space="preserve">Annahme KV Freizeitbetriebe/Gastro OÖ inkl. LNK</t>
+    <t xml:space="preserve">Ø lt. Blatt Stellenplan (inkl. Zuschläge, Dienstgeberanteil, Aushilfen)</t>
   </si>
   <si>
     <t xml:space="preserve">energie</t>
@@ -999,6 +1000,198 @@
   </si>
   <si>
     <t xml:space="preserve">Break-even in % der geplanten Besuche</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stellenbesetzungsplan Betreiber (Normaljahr, Gehälter = Annahmen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehälter orientiert am KV Hotel- und Gastgewerbe (Arbeiter/Angestellte) mit marktüblicher Überzahlung im Salzkammergut – vor Verwendung mit dem aktuell gültigen KV abgleichen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Öffnungsstunden pro Tag (10–22 Uhr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vor-/Nachbereitung pro Tag (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufheizen, Reinigung, Kassenabschluss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betriebstage pro Jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aus Annahmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betriebsstunden pro Jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wochenarbeitszeit (h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KV Hotel- und Gastgewerbe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urlaub (Wochen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Urlaubsgesetz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feiertage (Tage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gesetzliche Feiertage AT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Krankenstand (Tage, Ø)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netto-Jahresstunden je VZÄ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verfügbare Arbeitszeit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VZÄ je durchgehend besetzter Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faustregel: 1 Dauerposition ≈ 2,7 VZÄ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gehälter pro Jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inkl. Urlaubs- und Weihnachtsgeld</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuschläge Sonn-/Feiertag, Abend (in % der Bruttogehälter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7-Tage-Betrieb; Annahme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dienstgeberanteil (SV, DB, DZ, KommSt, MVK)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Richtwert AT ca. 28–30 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aushilfen / Geringfügige (pauschal, inkl. Abgaben)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spitzen: Wochenende, Events, Sommer-Kiosk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Funktion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brutto/Monat (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahresbrutto (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zuschläge (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DG-Anteil (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personalkosten (€)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø Besetzung je Betriebsstunde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufgaben / Einstufung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Betriebsleitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gesamtverantwortung, Personal, Budget, Marketing; Tagdienst + Rufbereitschaft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stv. Leitung / Gästeservice-Leitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dienstplanung, Kassa/Rezeption, Hotelkooperationen, Events</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haustechnik / Bademeister:in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wärmepumpe, Wasseraufbereitung, Saunaöfen, Holzofen; Bäderhygiene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saunameister:in – Teamleitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sauna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufgussplan, Event-Aufgüsse, Einschulung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saunameister:innen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aufgüsse, Aufsicht Saunabereich &amp; Steg, Erste Hilfe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rezeption / Kassa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gästeservice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check-in, Verkauf, Gutscheine, Telefon/Online</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laufende Reinigung Nass-/Ruhebereiche, Wäschelogistik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koch / Köchin (Regenerierküche)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service / Theke Bistro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theke, Bademantel-Bistro, im Sommer Kiosk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Summe Stammpersonal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aushilfen / Geringfügige</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PERSONALKOSTEN GESAMT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ø Personalkosten je VZÄ (→ Annahmen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Personalkosten in % vom Umsatz (aktives Szenario)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lesart Spalte I: Wie viele Personen dieser Funktion im Schnitt je Betriebsstunde im Haus sind. Summe ≈ 7–8 Personen gleichzeitig; Leitung/Technik arbeiten überwiegend im Tagdienst.</t>
   </si>
   <si>
     <t xml:space="preserve">Betreiber-GuV &amp; Pachtfluss – 10 Jahre (aktives Szenario, nominal)</t>
@@ -1170,14 +1363,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\);\-"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\);\-"/>
     <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
     <numFmt numFmtId="168" formatCode="0.0&quot; J.&quot;"/>
     <numFmt numFmtId="169" formatCode="0"/>
-    <numFmt numFmtId="170" formatCode="@"/>
+    <numFmt numFmtId="170" formatCode="0.0"/>
+    <numFmt numFmtId="171" formatCode="@"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -1334,7 +1528,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1431,6 +1625,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1467,7 +1669,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1854,15 +2072,15 @@
       </c>
       <c r="C8" s="4" t="n">
         <f aca="false">Betriebskosten!C13</f>
-        <v>1723301.75355906</v>
+        <v>1662815.55855906</v>
       </c>
       <c r="D8" s="4" t="n">
         <f aca="false">Betriebskosten!D13</f>
-        <v>1752636.11102732</v>
+        <v>1695030.21102732</v>
       </c>
       <c r="E8" s="4" t="n">
         <f aca="false">Betriebskosten!E13</f>
-        <v>1859371.49220854</v>
+        <v>1801765.59220854</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1894,15 +2112,15 @@
       </c>
       <c r="C10" s="4" t="n">
         <f aca="false">Betriebskosten!C16</f>
-        <v>-558127.600038476</v>
+        <v>-497641.405038476</v>
       </c>
       <c r="D10" s="4" t="n">
         <f aca="false">Betriebskosten!D16</f>
-        <v>-11489.2282262407</v>
+        <v>46116.6717737592</v>
       </c>
       <c r="E10" s="4" t="n">
         <f aca="false">Betriebskosten!E16</f>
-        <v>474759.803963063</v>
+        <v>532365.703963063</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1914,15 +2132,15 @@
       </c>
       <c r="C11" s="6" t="n">
         <f aca="false">Betriebskosten!C18</f>
-        <v>-0.424375432367209</v>
+        <v>-0.378384416775787</v>
       </c>
       <c r="D11" s="6" t="n">
         <f aca="false">Betriebskosten!D18</f>
-        <v>-0.00593878983201096</v>
+        <v>0.0238377387952543</v>
       </c>
       <c r="E11" s="6" t="n">
         <f aca="false">Betriebskosten!E18</f>
-        <v>0.183059035396843</v>
+        <v>0.205270857878738</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1934,15 +2152,15 @@
       </c>
       <c r="C12" s="4" t="n">
         <f aca="false">Betriebskosten!C24</f>
-        <v>57649.426244079</v>
+        <v>55222.8469556743</v>
       </c>
       <c r="D12" s="4" t="n">
         <f aca="false">Betriebskosten!D24</f>
-        <v>47525.9752987974</v>
+        <v>45490.4536776339</v>
       </c>
       <c r="E12" s="4" t="n">
         <f aca="false">Betriebskosten!E24</f>
-        <v>42122.2181054755</v>
+        <v>40290.9061930512</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1954,15 +2172,15 @@
       </c>
       <c r="C13" s="6" t="n">
         <f aca="false">Betriebskosten!C25</f>
-        <v>1.60137295122442</v>
+        <v>1.53396797099095</v>
       </c>
       <c r="D13" s="6" t="n">
         <f aca="false">Betriebskosten!D25</f>
-        <v>1.00861577459248</v>
+        <v>0.965417098421772</v>
       </c>
       <c r="E13" s="6" t="n">
         <f aca="false">Betriebskosten!E25</f>
-        <v>0.736209352538242</v>
+        <v>0.704201803601349</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2038,11 +2256,11 @@
       </c>
       <c r="D17" s="9" t="n">
         <f aca="false">MAX(0,Betriebskosten!D14/Umsatz!D16-Annahmen!$D$43)</f>
-        <v>0.014061210167989</v>
+        <v>0.0438377387952543</v>
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">MAX(0,Betriebskosten!E14/Umsatz!E16-Annahmen!$E$43)</f>
-        <v>0.203059035396843</v>
+        <v>0.225270857878738</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2058,11 +2276,11 @@
       </c>
       <c r="D18" s="4" t="n">
         <f aca="false">D17*Umsatz!D16</f>
-        <v>27202.9247248944</v>
+        <v>84808.8247248943</v>
       </c>
       <c r="E18" s="4" t="n">
         <f aca="false">E17*Umsatz!E16</f>
-        <v>526629.388322432</v>
+        <v>584235.288322432</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2776,10 +2994,12 @@
       <c r="B32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="24" t="n">
+        <f aca="false">D32+1</f>
         <v>21</v>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="25" t="n">
+        <f aca="false">Stellenplan!C29</f>
         <v>20</v>
       </c>
       <c r="E32" s="19" t="n">
@@ -2805,18 +3025,19 @@
       </c>
       <c r="C33" s="7" t="n">
         <f aca="false">D33</f>
-        <v>52000</v>
-      </c>
-      <c r="D33" s="16" t="n">
-        <v>52000</v>
+        <v>49119.705</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <f aca="false">Stellenplan!H32</f>
+        <v>49119.705</v>
       </c>
       <c r="E33" s="7" t="n">
         <f aca="false">D33</f>
-        <v>52000</v>
+        <v>49119.705</v>
       </c>
       <c r="F33" s="17" t="n">
         <f aca="false">INDEX(C33:E33,1,$C$4)</f>
-        <v>52000</v>
+        <v>49119.705</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>78</v>
@@ -2888,14 +3109,14 @@
       <c r="B36" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C36" s="24" t="n">
+      <c r="C36" s="26" t="n">
         <f aca="false">D36</f>
         <v>2.2</v>
       </c>
-      <c r="D36" s="25" t="n">
+      <c r="D36" s="27" t="n">
         <v>2.2</v>
       </c>
-      <c r="E36" s="24" t="n">
+      <c r="E36" s="26" t="n">
         <f aca="false">D36</f>
         <v>2.2</v>
       </c>
@@ -3009,14 +3230,14 @@
       <c r="B41" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="C41" s="26" t="n">
+      <c r="C41" s="28" t="n">
         <f aca="false">D41</f>
         <v>0.1</v>
       </c>
-      <c r="D41" s="27" t="n">
+      <c r="D41" s="29" t="n">
         <v>0.1</v>
       </c>
-      <c r="E41" s="26" t="n">
+      <c r="E41" s="28" t="n">
         <f aca="false">D41</f>
         <v>0.1</v>
       </c>
@@ -3222,18 +3443,18 @@
       <c r="B50" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C50" s="28" t="n">
+      <c r="C50" s="30" t="n">
         <f aca="false">D50</f>
         <v>2029</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="31" t="n">
         <v>2029</v>
       </c>
-      <c r="E50" s="28" t="n">
+      <c r="E50" s="30" t="n">
         <f aca="false">D50</f>
         <v>2029</v>
       </c>
-      <c r="F50" s="30" t="n">
+      <c r="F50" s="32" t="n">
         <f aca="false">INDEX(C50:E50,1,$C$4)</f>
         <v>2029</v>
       </c>
@@ -3608,7 +3829,7 @@
       <c r="A20" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="33" t="n">
         <f aca="false">SUM(B4:B19)</f>
         <v>1427</v>
       </c>
@@ -3617,7 +3838,7 @@
       <c r="A21" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="B21" s="25" t="n">
+      <c r="B21" s="27" t="n">
         <v>1.18</v>
       </c>
       <c r="D21" s="18" t="s">
@@ -3628,7 +3849,7 @@
       <c r="A22" s="12" t="s">
         <v>196</v>
       </c>
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="33" t="n">
         <f aca="false">ROUND(B20*B21,-1)</f>
         <v>1680</v>
       </c>
@@ -3759,7 +3980,7 @@
       <c r="B7" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="33" t="n">
         <f aca="false">SUM(F5:F6)</f>
         <v>300000</v>
       </c>
@@ -3803,7 +4024,7 @@
       <c r="B11" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="F11" s="31" t="n">
+      <c r="F11" s="33" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>1848000</v>
       </c>
@@ -3910,7 +4131,7 @@
       <c r="B18" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="F18" s="31" t="n">
+      <c r="F18" s="33" t="n">
         <f aca="false">SUM(F14:F17)</f>
         <v>2247000</v>
       </c>
@@ -4076,7 +4297,7 @@
       <c r="B28" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F28" s="31" t="n">
+      <c r="F28" s="33" t="n">
         <f aca="false">SUM(F21:F27)</f>
         <v>2768000</v>
       </c>
@@ -4180,7 +4401,7 @@
       <c r="B35" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="F35" s="31" t="n">
+      <c r="F35" s="33" t="n">
         <f aca="false">SUM(F31:F34)</f>
         <v>697000</v>
       </c>
@@ -4244,7 +4465,7 @@
       <c r="B40" s="12" t="s">
         <v>263</v>
       </c>
-      <c r="F40" s="31" t="n">
+      <c r="F40" s="33" t="n">
         <f aca="false">SUM(F38:F39)</f>
         <v>550000</v>
       </c>
@@ -4257,7 +4478,7 @@
       <c r="B42" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="F42" s="31" t="n">
+      <c r="F42" s="33" t="n">
         <f aca="false">F7+F11+F18+F28+F35+F40</f>
         <v>8410000</v>
       </c>
@@ -4306,7 +4527,7 @@
       <c r="B45" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E45" s="27" t="n">
+      <c r="E45" s="29" t="n">
         <v>0.12</v>
       </c>
       <c r="F45" s="7" t="n">
@@ -4321,7 +4542,7 @@
       <c r="B46" s="12" t="s">
         <v>274</v>
       </c>
-      <c r="F46" s="32" t="n">
+      <c r="F46" s="34" t="n">
         <f aca="false">F42+F43+F44+F45</f>
         <v>11114656</v>
       </c>
@@ -4395,7 +4616,7 @@
       <c r="B54" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="E54" s="27" t="n">
+      <c r="E54" s="29" t="n">
         <v>0.2</v>
       </c>
       <c r="F54" s="7" t="n">
@@ -4421,7 +4642,7 @@
       <c r="B56" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="F56" s="31" t="n">
+      <c r="F56" s="33" t="n">
         <f aca="false">SUM(F53:F55)</f>
         <v>2557431.2</v>
       </c>
@@ -4434,7 +4655,7 @@
       <c r="B58" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="F58" s="32" t="n">
+      <c r="F58" s="34" t="n">
         <f aca="false">F46-F56</f>
         <v>8557224.8</v>
       </c>
@@ -4554,19 +4775,19 @@
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="33" t="n">
         <f aca="false">C4+C5</f>
         <v>36000</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="33" t="n">
         <f aca="false">D4+D5</f>
         <v>47120</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="33" t="n">
         <f aca="false">E4+E5</f>
         <v>57215</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="33" t="n">
         <f aca="false">INDEX(C6:E6,1,Annahmen!$C$4)</f>
         <v>47120</v>
       </c>
@@ -4602,19 +4823,19 @@
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">(Annahmen!$C$16*Annahmen!$C$14+(1-Annahmen!$C$16)*Annahmen!$C$15)*(1-Annahmen!$C$17)</f>
         <v>25.6275</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">(Annahmen!$D$16*Annahmen!$D$14+(1-Annahmen!$D$16)*Annahmen!$D$15)*(1-Annahmen!$D$17)</f>
         <v>28.776</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">(Annahmen!$E$16*Annahmen!$E$14+(1-Annahmen!$E$16)*Annahmen!$E$15)*(1-Annahmen!$E$17)</f>
         <v>31.725</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="26" t="n">
         <f aca="false">INDEX(C8:E8,1,Annahmen!$C$4)</f>
         <v>28.776</v>
       </c>
@@ -4626,19 +4847,19 @@
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="26" t="n">
         <f aca="false">C8/(1+Annahmen!$C$18)</f>
         <v>22.679203539823</v>
       </c>
-      <c r="D9" s="24" t="n">
+      <c r="D9" s="26" t="n">
         <f aca="false">D8/(1+Annahmen!$D$18)</f>
         <v>25.4654867256637</v>
       </c>
-      <c r="E9" s="24" t="n">
+      <c r="E9" s="26" t="n">
         <f aca="false">E8/(1+Annahmen!$E$18)</f>
         <v>28.0752212389381</v>
       </c>
-      <c r="F9" s="24" t="n">
+      <c r="F9" s="26" t="n">
         <f aca="false">INDEX(C9:E9,1,Annahmen!$C$4)</f>
         <v>25.4654867256637</v>
       </c>
@@ -4770,19 +4991,19 @@
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">SUM(C11:C15)</f>
         <v>1315174.15352059</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="33" t="n">
         <f aca="false">SUM(D11:D15)</f>
         <v>1934607.64755675</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="33" t="n">
         <f aca="false">SUM(E11:E15)</f>
         <v>2593479.21796845</v>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="F16" s="33" t="n">
         <f aca="false">INDEX(C16:E16,1,Annahmen!$C$4)</f>
         <v>1934607.64755675</v>
       </c>
@@ -4794,19 +5015,19 @@
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="24" t="n">
+      <c r="C17" s="26" t="n">
         <f aca="false">C16/C6</f>
         <v>36.5326153755718</v>
       </c>
-      <c r="D17" s="24" t="n">
+      <c r="D17" s="26" t="n">
         <f aca="false">D16/D6</f>
         <v>41.0570383607121</v>
       </c>
-      <c r="E17" s="24" t="n">
+      <c r="E17" s="26" t="n">
         <f aca="false">E16/E6</f>
         <v>45.3286588826086</v>
       </c>
-      <c r="F17" s="24" t="n">
+      <c r="F17" s="26" t="n">
         <f aca="false">INDEX(C17:E17,1,Annahmen!$C$4)</f>
         <v>41.0570383607121</v>
       </c>
@@ -4917,19 +5138,19 @@
       </c>
       <c r="C6" s="7" t="n">
         <f aca="false">Annahmen!$C$32*Annahmen!$C$33</f>
-        <v>1092000</v>
+        <v>1031513.805</v>
       </c>
       <c r="D6" s="7" t="n">
         <f aca="false">Annahmen!$D$32*Annahmen!$D$33</f>
-        <v>1040000</v>
+        <v>982394.1</v>
       </c>
       <c r="E6" s="7" t="n">
         <f aca="false">Annahmen!$E$32*Annahmen!$E$33</f>
-        <v>1040000</v>
+        <v>982394.1</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">INDEX(C6:E6,1,Annahmen!$C$4)</f>
-        <v>1040000</v>
+        <v>982394.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5081,21 +5302,21 @@
         <v>314</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="31" t="n">
+      <c r="C13" s="33" t="n">
         <f aca="false">SUM(C4:C12)</f>
-        <v>1723301.75355906</v>
-      </c>
-      <c r="D13" s="31" t="n">
+        <v>1662815.55855906</v>
+      </c>
+      <c r="D13" s="33" t="n">
         <f aca="false">SUM(D4:D12)</f>
-        <v>1752636.11102732</v>
-      </c>
-      <c r="E13" s="31" t="n">
+        <v>1695030.21102732</v>
+      </c>
+      <c r="E13" s="33" t="n">
         <f aca="false">SUM(E4:E12)</f>
-        <v>1859371.49220854</v>
-      </c>
-      <c r="F13" s="31" t="n">
+        <v>1801765.59220854</v>
+      </c>
+      <c r="F13" s="33" t="n">
         <f aca="false">INDEX(C13:E13,1,Annahmen!$C$4)</f>
-        <v>1752636.11102732</v>
+        <v>1695030.21102732</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5103,21 +5324,21 @@
         <v>315</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="33" t="n">
         <f aca="false">Umsatz!C16-C13</f>
-        <v>-408127.600038476</v>
-      </c>
-      <c r="D14" s="31" t="n">
+        <v>-347641.405038476</v>
+      </c>
+      <c r="D14" s="33" t="n">
         <f aca="false">Umsatz!D16-D13</f>
-        <v>181971.536529435</v>
-      </c>
-      <c r="E14" s="31" t="n">
+        <v>239577.436529435</v>
+      </c>
+      <c r="E14" s="33" t="n">
         <f aca="false">Umsatz!E16-E13</f>
-        <v>734107.725759908</v>
-      </c>
-      <c r="F14" s="31" t="n">
+        <v>791713.625759908</v>
+      </c>
+      <c r="F14" s="33" t="n">
         <f aca="false">INDEX(C14:E14,1,Annahmen!$C$4)</f>
-        <v>181971.536529435</v>
+        <v>239577.436529435</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5125,19 +5346,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="31" t="n">
+      <c r="C15" s="33" t="n">
         <f aca="false">MAX(Annahmen!$C$42,Annahmen!$C$41*Umsatz!C16)</f>
         <v>150000</v>
       </c>
-      <c r="D15" s="31" t="n">
+      <c r="D15" s="33" t="n">
         <f aca="false">MAX(Annahmen!$D$42,Annahmen!$D$41*Umsatz!D16)</f>
         <v>193460.764755675</v>
       </c>
-      <c r="E15" s="31" t="n">
+      <c r="E15" s="33" t="n">
         <f aca="false">MAX(Annahmen!$E$42,Annahmen!$E$41*Umsatz!E16)</f>
         <v>259347.921796845</v>
       </c>
-      <c r="F15" s="31" t="n">
+      <c r="F15" s="33" t="n">
         <f aca="false">INDEX(C15:E15,1,Annahmen!$C$4)</f>
         <v>193460.764755675</v>
       </c>
@@ -5147,21 +5368,21 @@
         <v>316</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="33" t="n">
         <f aca="false">C14-C15</f>
-        <v>-558127.600038476</v>
-      </c>
-      <c r="D16" s="31" t="n">
+        <v>-497641.405038476</v>
+      </c>
+      <c r="D16" s="33" t="n">
         <f aca="false">D14-D15</f>
-        <v>-11489.2282262407</v>
-      </c>
-      <c r="E16" s="31" t="n">
+        <v>46116.6717737592</v>
+      </c>
+      <c r="E16" s="33" t="n">
         <f aca="false">E14-E15</f>
-        <v>474759.803963063</v>
-      </c>
-      <c r="F16" s="31" t="n">
+        <v>532365.703963063</v>
+      </c>
+      <c r="F16" s="33" t="n">
         <f aca="false">INDEX(C16:E16,1,Annahmen!$C$4)</f>
-        <v>-11489.2282262407</v>
+        <v>46116.6717737592</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5173,19 +5394,19 @@
       </c>
       <c r="C18" s="9" t="n">
         <f aca="false">C16/Umsatz!C16</f>
-        <v>-0.424375432367209</v>
+        <v>-0.378384416775787</v>
       </c>
       <c r="D18" s="9" t="n">
         <f aca="false">D16/Umsatz!D16</f>
-        <v>-0.00593878983201096</v>
+        <v>0.0238377387952543</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">E16/Umsatz!E16</f>
-        <v>0.183059035396843</v>
+        <v>0.205270857878738</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">INDEX(C18:E18,1,Annahmen!$C$4)</f>
-        <v>-0.00593878983201096</v>
+        <v>0.0238377387952543</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5197,19 +5418,19 @@
       </c>
       <c r="C19" s="9" t="n">
         <f aca="false">C6/Umsatz!C16</f>
-        <v>0.8303082881281</v>
+        <v>0.784317272536678</v>
       </c>
       <c r="D19" s="9" t="n">
         <f aca="false">D6/Umsatz!D16</f>
-        <v>0.537576702600878</v>
+        <v>0.507800173973612</v>
       </c>
       <c r="E19" s="9" t="n">
         <f aca="false">E6/Umsatz!E16</f>
-        <v>0.401005719573363</v>
+        <v>0.378793897091467</v>
       </c>
       <c r="F19" s="9" t="n">
         <f aca="false">INDEX(C19:E19,1,Annahmen!$C$4)</f>
-        <v>0.537576702600878</v>
+        <v>0.507800173973612</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5267,19 +5488,19 @@
       <c r="B22" s="3"/>
       <c r="C22" s="7" t="n">
         <f aca="false">C6+C7+C8+C12</f>
-        <v>1437000</v>
+        <v>1376513.805</v>
       </c>
       <c r="D22" s="7" t="n">
         <f aca="false">D6+D7+D8+D12</f>
-        <v>1345000</v>
+        <v>1287394.1</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">E6+E7+E8+E12</f>
-        <v>1325000</v>
+        <v>1267394.1</v>
       </c>
       <c r="F22" s="7" t="n">
         <f aca="false">INDEX(C22:E22,1,Annahmen!$C$4)</f>
-        <v>1345000</v>
+        <v>1287394.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5289,19 +5510,19 @@
       <c r="B23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C23" s="24" t="n">
+      <c r="C23" s="26" t="n">
         <f aca="false">(Umsatz!C16*(1-Annahmen!$C$41)-C4-C5-C9-C10-C11)/Umsatz!C6</f>
         <v>24.9265273502629</v>
       </c>
-      <c r="D23" s="24" t="n">
+      <c r="D23" s="26" t="n">
         <f aca="false">(Umsatz!D16*(1-Annahmen!$D$41)-D4-D5-D9-D10-D11)/Umsatz!D6</f>
         <v>28.3003134926519</v>
       </c>
-      <c r="E23" s="24" t="n">
+      <c r="E23" s="26" t="n">
         <f aca="false">(Umsatz!E16*(1-Annahmen!$E$41)-E4-E5-E9-E10-E11)/Umsatz!E6</f>
         <v>31.4560832642325</v>
       </c>
-      <c r="F23" s="24" t="n">
+      <c r="F23" s="26" t="n">
         <f aca="false">INDEX(C23:E23,1,Annahmen!$C$4)</f>
         <v>28.3003134926519</v>
       </c>
@@ -5315,19 +5536,19 @@
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">C22/C23</f>
-        <v>57649.426244079</v>
+        <v>55222.8469556743</v>
       </c>
       <c r="D24" s="7" t="n">
         <f aca="false">D22/D23</f>
-        <v>47525.9752987974</v>
+        <v>45490.4536776339</v>
       </c>
       <c r="E24" s="7" t="n">
         <f aca="false">E22/E23</f>
-        <v>42122.2181054755</v>
+        <v>40290.9061930512</v>
       </c>
       <c r="F24" s="7" t="n">
         <f aca="false">INDEX(C24:E24,1,Annahmen!$C$4)</f>
-        <v>47525.9752987974</v>
+        <v>45490.4536776339</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5339,19 +5560,19 @@
       </c>
       <c r="C25" s="9" t="n">
         <f aca="false">C24/Umsatz!C6</f>
-        <v>1.60137295122442</v>
+        <v>1.53396797099095</v>
       </c>
       <c r="D25" s="9" t="n">
         <f aca="false">D24/Umsatz!D6</f>
-        <v>1.00861577459248</v>
+        <v>0.965417098421772</v>
       </c>
       <c r="E25" s="9" t="n">
         <f aca="false">E24/Umsatz!E6</f>
-        <v>0.736209352538242</v>
+        <v>0.704201803601349</v>
       </c>
       <c r="F25" s="9" t="n">
         <f aca="false">INDEX(C25:E25,1,Annahmen!$C$4)</f>
-        <v>1.00861577459248</v>
+        <v>0.965417098421772</v>
       </c>
     </row>
   </sheetData>
@@ -5370,6 +5591,649 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:J35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="35" t="s">
+        <v>325</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B4" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <f aca="false">Annahmen!$D$8+Annahmen!$D$9</f>
+        <v>351</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <f aca="false">(B4+B5)*B6</f>
+        <v>4563</v>
+      </c>
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B8" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="J8" s="18" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B9" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="16" t="n">
+        <v>13</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B11" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="B12" s="7" t="n">
+        <f aca="false">B8*52-B9*B8-(B10+B11)*B8/5</f>
+        <v>1696</v>
+      </c>
+      <c r="J12" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="B13" s="26" t="n">
+        <f aca="false">B7/B12</f>
+        <v>2.69044811320755</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B14" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" s="18" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B15" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B16" s="20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J16" s="18" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="B17" s="16" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C20" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="16" t="n">
+        <v>4300</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <f aca="false">C20*D20*$B$14</f>
+        <v>60200</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <f aca="false">E20*$B$15</f>
+        <v>3612</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <f aca="false">(E20+F20)*$B$16</f>
+        <v>18505.48</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <f aca="false">E20+F20+G20</f>
+        <v>82317.48</v>
+      </c>
+      <c r="I20" s="26" t="n">
+        <f aca="false">C20*$B$12/$B$7</f>
+        <v>0.371685294762218</v>
+      </c>
+      <c r="J20" s="18" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C21" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="16" t="n">
+        <v>3200</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <f aca="false">C21*D21*$B$14</f>
+        <v>44800</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <f aca="false">E21*$B$15</f>
+        <v>2688</v>
+      </c>
+      <c r="G21" s="7" t="n">
+        <f aca="false">(E21+F21)*$B$16</f>
+        <v>13771.52</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <f aca="false">E21+F21+G21</f>
+        <v>61259.52</v>
+      </c>
+      <c r="I21" s="26" t="n">
+        <f aca="false">C21*$B$12/$B$7</f>
+        <v>0.371685294762218</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C22" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <f aca="false">C22*D22*$B$14</f>
+        <v>43400</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <f aca="false">E22*$B$15</f>
+        <v>2604</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <f aca="false">(E22+F22)*$B$16</f>
+        <v>13341.16</v>
+      </c>
+      <c r="H22" s="7" t="n">
+        <f aca="false">E22+F22+G22</f>
+        <v>59345.16</v>
+      </c>
+      <c r="I22" s="26" t="n">
+        <f aca="false">C22*$B$12/$B$7</f>
+        <v>0.371685294762218</v>
+      </c>
+      <c r="J22" s="18" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C23" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>2850</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <f aca="false">C23*D23*$B$14</f>
+        <v>39900</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <f aca="false">E23*$B$15</f>
+        <v>2394</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <f aca="false">(E23+F23)*$B$16</f>
+        <v>12265.26</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <f aca="false">E23+F23+G23</f>
+        <v>54559.26</v>
+      </c>
+      <c r="I23" s="26" t="n">
+        <f aca="false">C23*$B$12/$B$7</f>
+        <v>0.371685294762218</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="C24" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <f aca="false">C24*D24*$B$14</f>
+        <v>140000</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <f aca="false">E24*$B$15</f>
+        <v>8400</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <f aca="false">(E24+F24)*$B$16</f>
+        <v>43036</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <f aca="false">E24+F24+G24</f>
+        <v>191436</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <f aca="false">C24*$B$12/$B$7</f>
+        <v>1.48674117904887</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C25" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" s="16" t="n">
+        <v>2200</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <f aca="false">C25*D25*$B$14</f>
+        <v>123200</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <f aca="false">E25*$B$15</f>
+        <v>7392</v>
+      </c>
+      <c r="G25" s="7" t="n">
+        <f aca="false">(E25+F25)*$B$16</f>
+        <v>37871.68</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <f aca="false">E25+F25+G25</f>
+        <v>168463.68</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <f aca="false">C25*$B$12/$B$7</f>
+        <v>1.48674117904887</v>
+      </c>
+      <c r="J25" s="18" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="C26" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="16" t="n">
+        <v>2050</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <f aca="false">C26*D26*$B$14</f>
+        <v>86100</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <f aca="false">E26*$B$15</f>
+        <v>5166</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <f aca="false">(E26+F26)*$B$16</f>
+        <v>26467.14</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <f aca="false">E26+F26+G26</f>
+        <v>117733.14</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <f aca="false">C26*$B$12/$B$7</f>
+        <v>1.11505588428665</v>
+      </c>
+      <c r="J26" s="18" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C27" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>2450</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <f aca="false">C27*D27*$B$14</f>
+        <v>68600</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <f aca="false">E27*$B$15</f>
+        <v>4116</v>
+      </c>
+      <c r="G27" s="7" t="n">
+        <f aca="false">(E27+F27)*$B$16</f>
+        <v>21087.64</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <f aca="false">E27+F27+G27</f>
+        <v>93803.64</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <f aca="false">C27*$B$12/$B$7</f>
+        <v>0.743370589524436</v>
+      </c>
+      <c r="J27" s="18" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="C28" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="16" t="n">
+        <v>2150</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <f aca="false">C28*D28*$B$14</f>
+        <v>90300</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <f aca="false">E28*$B$15</f>
+        <v>5418</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <f aca="false">(E28+F28)*$B$16</f>
+        <v>27758.22</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <f aca="false">E28+F28+G28</f>
+        <v>123476.22</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <f aca="false">C28*$B$12/$B$7</f>
+        <v>1.11505588428665</v>
+      </c>
+      <c r="J28" s="18" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="12" t="s">
+        <v>382</v>
+      </c>
+      <c r="C29" s="37" t="n">
+        <f aca="false">SUM(C20:C28)</f>
+        <v>20</v>
+      </c>
+      <c r="E29" s="33" t="n">
+        <f aca="false">SUM(E20:E28)</f>
+        <v>696500</v>
+      </c>
+      <c r="F29" s="33" t="n">
+        <f aca="false">SUM(F20:F28)</f>
+        <v>41790</v>
+      </c>
+      <c r="G29" s="33" t="n">
+        <f aca="false">SUM(G20:G28)</f>
+        <v>214104.1</v>
+      </c>
+      <c r="H29" s="33" t="n">
+        <f aca="false">SUM(H20:H28)</f>
+        <v>952394.1</v>
+      </c>
+      <c r="I29" s="38" t="n">
+        <f aca="false">SUM(I20:I28)</f>
+        <v>7.43370589524436</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="H30" s="7" t="n">
+        <f aca="false">B17</f>
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="12" t="s">
+        <v>384</v>
+      </c>
+      <c r="H31" s="34" t="n">
+        <f aca="false">H29+H30</f>
+        <v>982394.1</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <f aca="false">H31/C29</f>
+        <v>49119.705</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="H33" s="9" t="n">
+        <f aca="false">H31/Umsatz!F16</f>
+        <v>0.507800173973612</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>387</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:J2"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5379,7 +6243,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>388</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5393,84 +6257,84 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>325</v>
+        <v>389</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>326</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>327</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>328</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>329</v>
+        <v>393</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>330</v>
+        <v>394</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>331</v>
+        <v>395</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>332</v>
+        <v>396</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>333</v>
+        <v>397</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>334</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="B5" s="33" t="str">
+        <v>399</v>
+      </c>
+      <c r="B5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+0,"0")</f>
         <v>2029</v>
       </c>
-      <c r="C5" s="33" t="str">
+      <c r="C5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+1,"0")</f>
         <v>2030</v>
       </c>
-      <c r="D5" s="33" t="str">
+      <c r="D5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+2,"0")</f>
         <v>2031</v>
       </c>
-      <c r="E5" s="33" t="str">
+      <c r="E5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+3,"0")</f>
         <v>2032</v>
       </c>
-      <c r="F5" s="33" t="str">
+      <c r="F5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+4,"0")</f>
         <v>2033</v>
       </c>
-      <c r="G5" s="33" t="str">
+      <c r="G5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+5,"0")</f>
         <v>2034</v>
       </c>
-      <c r="H5" s="33" t="str">
+      <c r="H5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+6,"0")</f>
         <v>2035</v>
       </c>
-      <c r="I5" s="33" t="str">
+      <c r="I5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+7,"0")</f>
         <v>2036</v>
       </c>
-      <c r="J5" s="33" t="str">
+      <c r="J5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+8,"0")</f>
         <v>2037</v>
       </c>
-      <c r="K5" s="33" t="str">
+      <c r="K5" s="39" t="str">
         <f aca="false">TEXT(Annahmen!$F$50+9,"0")</f>
         <v>2038</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>336</v>
+        <v>400</v>
       </c>
       <c r="B6" s="9" t="n">
         <f aca="false">Annahmen!$F$51</f>
@@ -5515,90 +6379,90 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="B7" s="24" t="n">
+        <v>401</v>
+      </c>
+      <c r="B7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^0</f>
         <v>1</v>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^1</f>
         <v>1.025</v>
       </c>
-      <c r="D7" s="24" t="n">
+      <c r="D7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^2</f>
         <v>1.050625</v>
       </c>
-      <c r="E7" s="24" t="n">
+      <c r="E7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^3</f>
         <v>1.076890625</v>
       </c>
-      <c r="F7" s="24" t="n">
+      <c r="F7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^4</f>
         <v>1.103812890625</v>
       </c>
-      <c r="G7" s="24" t="n">
+      <c r="G7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^5</f>
         <v>1.13140821289062</v>
       </c>
-      <c r="H7" s="24" t="n">
+      <c r="H7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^6</f>
         <v>1.15969341821289</v>
       </c>
-      <c r="I7" s="24" t="n">
+      <c r="I7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^7</f>
         <v>1.18868575366821</v>
       </c>
-      <c r="J7" s="24" t="n">
+      <c r="J7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^8</f>
         <v>1.21840289750992</v>
       </c>
-      <c r="K7" s="24" t="n">
+      <c r="K7" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$53)^9</f>
         <v>1.24886296994767</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B8" s="24" t="n">
+        <v>402</v>
+      </c>
+      <c r="B8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^0</f>
         <v>1</v>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^1</f>
         <v>1.03</v>
       </c>
-      <c r="D8" s="24" t="n">
+      <c r="D8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^2</f>
         <v>1.0609</v>
       </c>
-      <c r="E8" s="24" t="n">
+      <c r="E8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^3</f>
         <v>1.092727</v>
       </c>
-      <c r="F8" s="24" t="n">
+      <c r="F8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^4</f>
         <v>1.12550881</v>
       </c>
-      <c r="G8" s="24" t="n">
+      <c r="G8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^5</f>
         <v>1.1592740743</v>
       </c>
-      <c r="H8" s="24" t="n">
+      <c r="H8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^6</f>
         <v>1.194052296529</v>
       </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^7</f>
         <v>1.22987386542487</v>
       </c>
-      <c r="J8" s="24" t="n">
+      <c r="J8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^8</f>
         <v>1.26677008138762</v>
       </c>
-      <c r="K8" s="24" t="n">
+      <c r="K8" s="26" t="n">
         <f aca="false">(1+Annahmen!$F$54)^9</f>
         <v>1.30477318382925</v>
       </c>
@@ -5652,50 +6516,50 @@
       <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="33" t="n">
         <f aca="false">Umsatz!F16*B6*B7</f>
         <v>1450955.73566756</v>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C10" s="33" t="n">
         <f aca="false">Umsatz!F16*C6*C7</f>
         <v>1784675.5548711</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D10" s="33" t="n">
         <f aca="false">Umsatz!F16*D6*D7</f>
         <v>2032547.15971431</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E10" s="33" t="n">
         <f aca="false">Umsatz!F16*E6*E7</f>
         <v>2083360.83870717</v>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="F10" s="33" t="n">
         <f aca="false">Umsatz!F16*F6*F7</f>
         <v>2135444.85967485</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G10" s="33" t="n">
         <f aca="false">Umsatz!F16*G6*G7</f>
         <v>2188830.98116672</v>
       </c>
-      <c r="H10" s="31" t="n">
+      <c r="H10" s="33" t="n">
         <f aca="false">Umsatz!F16*H6*H7</f>
         <v>2243551.75569589</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I10" s="33" t="n">
         <f aca="false">Umsatz!F16*I6*I7</f>
         <v>2299640.54958829</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="33" t="n">
         <f aca="false">Umsatz!F16*J6*J7</f>
         <v>2357131.56332799</v>
       </c>
-      <c r="K10" s="31" t="n">
+      <c r="K10" s="33" t="n">
         <f aca="false">Umsatz!F16*K6*K7</f>
         <v>2416059.85241119</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>339</v>
+        <v>403</v>
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*B6*B8</f>
@@ -5744,93 +6608,93 @@
       </c>
       <c r="B12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*B8</f>
-        <v>1345000</v>
+        <v>1287394.1</v>
       </c>
       <c r="C12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*C8</f>
-        <v>1385350</v>
+        <v>1326015.923</v>
       </c>
       <c r="D12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*D8</f>
-        <v>1426910.5</v>
+        <v>1365796.40069</v>
       </c>
       <c r="E12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*E8</f>
-        <v>1469717.815</v>
+        <v>1406770.2927107</v>
       </c>
       <c r="F12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*F8</f>
-        <v>1513809.34945</v>
+        <v>1448973.40149202</v>
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*G8</f>
-        <v>1559223.6299335</v>
+        <v>1492442.60353678</v>
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*H8</f>
-        <v>1606000.33883151</v>
+        <v>1537215.88164289</v>
       </c>
       <c r="I12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*I8</f>
-        <v>1654180.34899645</v>
+        <v>1583332.35809217</v>
       </c>
       <c r="J12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*J8</f>
-        <v>1703805.75946634</v>
+        <v>1630832.32883494</v>
       </c>
       <c r="K12" s="7" t="n">
         <f aca="false">Betriebskosten!F22*K8</f>
-        <v>1754919.93225033</v>
+        <v>1679757.29869999</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>340</v>
+        <v>404</v>
       </c>
       <c r="B13" s="7" t="n">
         <f aca="false">B10-B11-B12</f>
-        <v>-199771.347602924</v>
+        <v>-142165.447602924</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">C10-C11-C12</f>
-        <v>21446.8799487804</v>
+        <v>80780.9569487802</v>
       </c>
       <c r="D13" s="7" t="n">
         <f aca="false">D10-D11-D12</f>
-        <v>173175.509525432</v>
+        <v>234289.608835432</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">E10-E11-E12</f>
-        <v>168208.039012622</v>
+        <v>231155.561301922</v>
       </c>
       <c r="F13" s="7" t="n">
         <f aca="false">F10-F11-F12</f>
-        <v>162837.475989464</v>
+        <v>227673.423947443</v>
       </c>
       <c r="G13" s="7" t="n">
         <f aca="false">G10-G11-G12</f>
-        <v>157045.375970774</v>
+        <v>223826.402367493</v>
       </c>
       <c r="H13" s="7" t="n">
         <f aca="false">H10-H11-H12</f>
-        <v>150812.582344064</v>
+        <v>219597.039532684</v>
       </c>
       <c r="I13" s="7" t="n">
         <f aca="false">I10-I11-I12</f>
-        <v>144119.201035906</v>
+        <v>214967.191940184</v>
       </c>
       <c r="J13" s="7" t="n">
         <f aca="false">J10-J11-J12</f>
-        <v>136944.574319041</v>
+        <v>209918.004950448</v>
       </c>
       <c r="K13" s="7" t="n">
         <f aca="false">K10-K11-K12</f>
-        <v>129267.253731972</v>
+        <v>204429.887282321</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>341</v>
+        <v>405</v>
       </c>
       <c r="B14" s="7" t="n">
         <f aca="false">MAX(Annahmen!$F$42*B8,Annahmen!$F$41*B10)</f>
@@ -5877,90 +6741,90 @@
       <c r="A15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="31" t="n">
+      <c r="B15" s="33" t="n">
         <f aca="false">B13-B14</f>
-        <v>-349771.347602924</v>
-      </c>
-      <c r="C15" s="31" t="n">
+        <v>-292165.447602924</v>
+      </c>
+      <c r="C15" s="33" t="n">
         <f aca="false">C13-C14</f>
-        <v>-157020.67553833</v>
-      </c>
-      <c r="D15" s="31" t="n">
+        <v>-97686.5985383302</v>
+      </c>
+      <c r="D15" s="33" t="n">
         <f aca="false">D13-D14</f>
-        <v>-30079.2064459998</v>
-      </c>
-      <c r="E15" s="31" t="n">
+        <v>31034.8928640002</v>
+      </c>
+      <c r="E15" s="33" t="n">
         <f aca="false">E13-E14</f>
-        <v>-40128.0448580948</v>
-      </c>
-      <c r="F15" s="31" t="n">
+        <v>22819.4774312051</v>
+      </c>
+      <c r="F15" s="33" t="n">
         <f aca="false">F13-F14</f>
-        <v>-50707.0099780205</v>
-      </c>
-      <c r="G15" s="31" t="n">
+        <v>14128.9379799583</v>
+      </c>
+      <c r="G15" s="33" t="n">
         <f aca="false">G13-G14</f>
-        <v>-61837.7221458978</v>
-      </c>
-      <c r="H15" s="31" t="n">
+        <v>4943.30425082057</v>
+      </c>
+      <c r="H15" s="33" t="n">
         <f aca="false">H13-H14</f>
-        <v>-73542.5932255253</v>
-      </c>
-      <c r="I15" s="31" t="n">
+        <v>-4758.13603690534</v>
+      </c>
+      <c r="I15" s="33" t="n">
         <f aca="false">I13-I14</f>
-        <v>-85844.8539229228</v>
-      </c>
-      <c r="J15" s="31" t="n">
+        <v>-14996.8630186444</v>
+      </c>
+      <c r="J15" s="33" t="n">
         <f aca="false">J13-J14</f>
-        <v>-98768.5820137584</v>
-      </c>
-      <c r="K15" s="31" t="n">
+        <v>-25795.1513823515</v>
+      </c>
+      <c r="K15" s="33" t="n">
         <f aca="false">K13-K14</f>
-        <v>-112338.731509147</v>
+        <v>-37176.097958798</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>342</v>
+        <v>406</v>
       </c>
       <c r="B16" s="7" t="n">
         <f aca="false">B15</f>
-        <v>-349771.347602924</v>
+        <v>-292165.447602924</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">B16+C15</f>
-        <v>-506792.023141254</v>
+        <v>-389852.046141254</v>
       </c>
       <c r="D16" s="7" t="n">
         <f aca="false">C16+D15</f>
-        <v>-536871.229587254</v>
+        <v>-358817.153277254</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">D16+E15</f>
-        <v>-576999.274445349</v>
+        <v>-335997.675846049</v>
       </c>
       <c r="F16" s="7" t="n">
         <f aca="false">E16+F15</f>
-        <v>-627706.284423369</v>
+        <v>-321868.737866091</v>
       </c>
       <c r="G16" s="7" t="n">
         <f aca="false">F16+G15</f>
-        <v>-689544.006569267</v>
+        <v>-316925.43361527</v>
       </c>
       <c r="H16" s="7" t="n">
         <f aca="false">G16+H15</f>
-        <v>-763086.599794792</v>
+        <v>-321683.569652176</v>
       </c>
       <c r="I16" s="7" t="n">
         <f aca="false">H16+I15</f>
-        <v>-848931.453717715</v>
+        <v>-336680.43267082</v>
       </c>
       <c r="J16" s="7" t="n">
         <f aca="false">I16+J15</f>
-        <v>-947700.035731474</v>
+        <v>-362475.584053172</v>
       </c>
       <c r="K16" s="7" t="n">
         <f aca="false">J16+K15</f>
-        <v>-1060038.76724062</v>
+        <v>-399651.68201197</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5970,7 +6834,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>343</v>
+        <v>407</v>
       </c>
       <c r="B18" s="7" t="n">
         <f aca="false">B14</f>
@@ -6015,7 +6879,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>344</v>
+        <v>408</v>
       </c>
       <c r="B19" s="7" t="n">
         <f aca="false">-Investition!$F$49*Annahmen!$F$45*B8</f>
@@ -6060,7 +6924,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="B20" s="7" t="n">
         <f aca="false">-Annahmen!$F$46*B8</f>
@@ -6105,52 +6969,52 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="B21" s="31" t="n">
+        <v>410</v>
+      </c>
+      <c r="B21" s="33" t="n">
         <f aca="false">SUM(B18:B20)</f>
         <v>70096</v>
       </c>
-      <c r="C21" s="31" t="n">
+      <c r="C21" s="33" t="n">
         <f aca="false">SUM(C18:C20)</f>
         <v>96166.4354871105</v>
       </c>
-      <c r="D21" s="31" t="n">
+      <c r="D21" s="33" t="n">
         <f aca="false">SUM(D18:D20)</f>
         <v>118484.562371431</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="33" t="n">
         <f aca="false">SUM(E18:E20)</f>
         <v>121022.825662717</v>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="F21" s="33" t="n">
         <f aca="false">SUM(F18:F20)</f>
         <v>123611.830013245</v>
       </c>
-      <c r="G21" s="31" t="n">
+      <c r="G21" s="33" t="n">
         <f aca="false">SUM(G18:G20)</f>
         <v>126252.462483805</v>
       </c>
-      <c r="H21" s="31" t="n">
+      <c r="H21" s="33" t="n">
         <f aca="false">SUM(H18:H20)</f>
         <v>128945.620867736</v>
       </c>
-      <c r="I21" s="31" t="n">
+      <c r="I21" s="33" t="n">
         <f aca="false">SUM(I18:I20)</f>
         <v>131692.21361592</v>
       </c>
-      <c r="J21" s="31" t="n">
+      <c r="J21" s="33" t="n">
         <f aca="false">SUM(J18:J20)</f>
         <v>134493.159749603</v>
       </c>
-      <c r="K21" s="31" t="n">
+      <c r="K21" s="33" t="n">
         <f aca="false">SUM(K18:K20)</f>
         <v>137349.388760427</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>347</v>
+        <v>411</v>
       </c>
       <c r="B22" s="7" t="n">
         <f aca="false">B21</f>
@@ -6195,52 +7059,52 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>348</v>
+        <v>412</v>
       </c>
       <c r="B23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*B8</f>
-        <v>23712</v>
+        <v>22398.58548</v>
       </c>
       <c r="C23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*C8</f>
-        <v>24423.36</v>
+        <v>23070.5430444</v>
       </c>
       <c r="D23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*D8</f>
-        <v>25156.0608</v>
+        <v>23762.659335732</v>
       </c>
       <c r="E23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*E8</f>
-        <v>25910.742624</v>
+        <v>24475.539115804</v>
       </c>
       <c r="F23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*F8</f>
-        <v>26688.06490272</v>
+        <v>25209.8052892781</v>
       </c>
       <c r="G23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*G8</f>
-        <v>27488.7068498016</v>
+        <v>25966.0994479564</v>
       </c>
       <c r="H23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*H8</f>
-        <v>28313.3680552957</v>
+        <v>26745.0824313951</v>
       </c>
       <c r="I23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*I8</f>
-        <v>29162.7690969545</v>
+        <v>27547.434904337</v>
       </c>
       <c r="J23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*J8</f>
-        <v>30037.6521698632</v>
+        <v>28373.8579514671</v>
       </c>
       <c r="K23" s="7" t="n">
         <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*K8</f>
-        <v>30938.7817349591</v>
+        <v>29225.0736900111</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>349</v>
+        <v>413</v>
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">SUM(B21:K21)</f>
@@ -6249,7 +7113,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>350</v>
+        <v>414</v>
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">B25/Investition!$F$58</f>
@@ -6267,7 +7131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -6287,24 +7151,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>351</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="34" t="s">
-        <v>352</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="A2" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>353</v>
+        <v>417</v>
       </c>
       <c r="D4" s="4" t="n">
         <f aca="false">Investition!$F$58</f>
@@ -6313,63 +7177,63 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D5" s="27" t="n">
+        <v>418</v>
+      </c>
+      <c r="D5" s="29" t="n">
         <v>0.1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>355</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="D6" s="27" t="n">
+        <v>420</v>
+      </c>
+      <c r="D6" s="29" t="n">
         <v>0.15</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="D7" s="27" t="n">
+        <v>422</v>
+      </c>
+      <c r="D7" s="29" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>360</v>
+        <v>424</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>361</v>
+        <v>425</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>362</v>
+        <v>426</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>363</v>
+        <v>427</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>364</v>
+        <v>428</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>365</v>
+        <v>429</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>366</v>
+        <v>430</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>431</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>5700</v>
@@ -6377,7 +7241,7 @@
       <c r="C10" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="D10" s="35"/>
+      <c r="D10" s="41"/>
       <c r="E10" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B10/$B$17+(1-$D$7)*C10/$C$17)+IF(D10="x",$D$6,0)</f>
         <v>0.184313933729822</v>
@@ -6397,7 +7261,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>368</v>
+        <v>432</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>3500</v>
@@ -6405,7 +7269,7 @@
       <c r="C11" s="19" t="n">
         <v>45000</v>
       </c>
-      <c r="D11" s="35"/>
+      <c r="D11" s="41"/>
       <c r="E11" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B11/$B$17+(1-$D$7)*C11/$C$17)+IF(D11="x",$D$6,0)</f>
         <v>0.112457519116398</v>
@@ -6425,7 +7289,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>369</v>
+        <v>433</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>1650</v>
@@ -6433,8 +7297,8 @@
       <c r="C12" s="19" t="n">
         <v>120000</v>
       </c>
-      <c r="D12" s="35" t="s">
-        <v>370</v>
+      <c r="D12" s="41" t="s">
+        <v>434</v>
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B12/$B$17+(1-$D$7)*C12/$C$17)+IF(D12="x",$D$6,0)</f>
@@ -6455,7 +7319,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>371</v>
+        <v>435</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>1600</v>
@@ -6463,7 +7327,7 @@
       <c r="C13" s="19" t="n">
         <v>100000</v>
       </c>
-      <c r="D13" s="35"/>
+      <c r="D13" s="41"/>
       <c r="E13" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B13/$B$17+(1-$D$7)*C13/$C$17)+IF(D13="x",$D$6,0)</f>
         <v>0.105564995751912</v>
@@ -6483,7 +7347,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>372</v>
+        <v>436</v>
       </c>
       <c r="B14" s="19" t="n">
         <v>1550</v>
@@ -6491,7 +7355,7 @@
       <c r="C14" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="D14" s="35"/>
+      <c r="D14" s="41"/>
       <c r="E14" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B14/$B$17+(1-$D$7)*C14/$C$17)+IF(D14="x",$D$6,0)</f>
         <v>0.0873513169073917</v>
@@ -6511,7 +7375,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>373</v>
+        <v>437</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>1200</v>
@@ -6519,7 +7383,7 @@
       <c r="C15" s="19" t="n">
         <v>70000</v>
       </c>
-      <c r="D15" s="35"/>
+      <c r="D15" s="41"/>
       <c r="E15" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B15/$B$17+(1-$D$7)*C15/$C$17)+IF(D15="x",$D$6,0)</f>
         <v>0.0757646559048428</v>
@@ -6539,7 +7403,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>374</v>
+        <v>438</v>
       </c>
       <c r="B16" s="19" t="n">
         <v>850</v>
@@ -6547,7 +7411,7 @@
       <c r="C16" s="19" t="n">
         <v>65000</v>
       </c>
-      <c r="D16" s="35"/>
+      <c r="D16" s="41"/>
       <c r="E16" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B16/$B$17+(1-$D$7)*C16/$C$17)+IF(D16="x",$D$6,0)</f>
         <v>0.064177994902294</v>
@@ -6567,36 +7431,36 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="B17" s="31" t="n">
+        <v>439</v>
+      </c>
+      <c r="B17" s="33" t="n">
         <f aca="false">SUM(B10:B16)</f>
         <v>16050</v>
       </c>
-      <c r="C17" s="31" t="n">
+      <c r="C17" s="33" t="n">
         <f aca="false">SUM(C10:C16)</f>
         <v>550000</v>
       </c>
-      <c r="E17" s="36" t="n">
+      <c r="E17" s="42" t="n">
         <f aca="false">SUM(E10:E16)</f>
         <v>0.9</v>
       </c>
-      <c r="F17" s="31" t="n">
+      <c r="F17" s="33" t="n">
         <f aca="false">SUM(F10:F16)</f>
         <v>7701502.32</v>
       </c>
-      <c r="G17" s="31" t="n">
+      <c r="G17" s="33" t="n">
         <f aca="false">SUM(G10:G16)</f>
         <v>118811.449901199</v>
       </c>
-      <c r="H17" s="31" t="n">
+      <c r="H17" s="33" t="n">
         <f aca="false">F17/B17</f>
         <v>479.844381308411</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>376</v>
+        <v>440</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">D5</f>
@@ -6609,7 +7473,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>377</v>
+        <v>441</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">E17+E18</f>
@@ -6626,7 +7490,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>378</v>
+        <v>442</v>
       </c>
     </row>
   </sheetData>

--- a/seesauna-attersee/Rechenmodell_Seesauna_Attersee.xlsx
+++ b/seesauna-attersee/Rechenmodell_Seesauna_Attersee.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="464">
   <si>
     <t xml:space="preserve">Szenarienvergleich – Normaljahr</t>
   </si>
@@ -183,6 +183,15 @@
     <t xml:space="preserve">120 gleichzeitig × ~2,5 Wechsel</t>
   </si>
   <si>
+    <t xml:space="preserve">oeff_verl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besuchsverlust durch gestaffelte Öffnung (Mo–Do erst ab 14 Uhr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annahme; Vormittage unter der Woche schwach frequentiert</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preise (brutto, inkl. USt)</t>
   </si>
   <si>
@@ -237,7 +246,7 @@
     <t xml:space="preserve">Gastro-Umsatz pro Besucher (brutto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Branchenüblich 8–15 € (Bistro, kleine Karte)</t>
+    <t xml:space="preserve">Smart-Fridge mit Fertigprodukten (z. B. matty) + Kaffee-/Getränkeautomat; Bistro mit Service wäre 11–14 €</t>
   </si>
   <si>
     <t xml:space="preserve">ust_g</t>
@@ -255,7 +264,7 @@
     <t xml:space="preserve">Wareneinsatzquote Gastro</t>
   </si>
   <si>
-    <t xml:space="preserve">Branchenwert Bistro 28–35 %</t>
+    <t xml:space="preserve">Fertigprodukte inkl. Automaten-/Systemgebühr; Bistro mit Küche wäre 28–35 %</t>
   </si>
   <si>
     <t xml:space="preserve">kiosk</t>
@@ -393,6 +402,39 @@
     <t xml:space="preserve">Verwaltung, Versicherung, IT, Beratung</t>
   </si>
   <si>
+    <t xml:space="preserve">rein_ext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinigung Fremdfirma (nachts)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annahme: ~6 Mannstunden/Nacht × 365 + Grundreinigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aufg_hon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Event-Aufgüsse freie Saunameister:innen (Honorar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annahme: Wochenende/Ferien ~200 Aufgüsse × ~120 €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tech_ext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technik-Wartungsvertrag + Fernüberwachung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lüftung, WP, Wasseraufbereitung, Saunaöfen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it_auto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizenzen Ticketing/Zutritt/Smart-Fridge, Zahlungsgebühren</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pachtvertrag (Gemeinde-GmbH → Betreiber)</t>
   </si>
   <si>
@@ -516,10 +558,10 @@
     <t xml:space="preserve">Erläuterung</t>
   </si>
   <si>
-    <t xml:space="preserve">Eingang, Kassa, Shop-Ecke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zutrittssystem mit Chip-Armband, Gutscheinverkauf</t>
+    <t xml:space="preserve">Eingang, Empfang, Kiosk-Terminals, Drehkreuze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Online-Ticket/QR, RFID-Armband; Empfang nur zu Spitzenzeiten besetzt</t>
   </si>
   <si>
     <t xml:space="preserve">Garderobe &amp; Umkleiden (Spinde)</t>
@@ -576,16 +618,16 @@
     <t xml:space="preserve">50 Liegen, Kamin, Bibliothek</t>
   </si>
   <si>
-    <t xml:space="preserve">Bistro (Gastraum + Theke)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Im Bademantel; Terrasse saisonal zusätzlich</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bistro-Küche (Regenerierküche) &amp; Lager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kleine Karte, 3–4 warme Gerichte</t>
+    <t xml:space="preserve">Bistro-Lounge mit Smart-Fridges &amp; Automaten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selbstbedienung, Zahlung per Armband; Terrasse saisonal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gastro-Lager, Warenannahme, Spüle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fertigprodukte; Fläche als Reserve für spätere Küche</t>
   </si>
   <si>
     <t xml:space="preserve">Massage-/Behandlungsräume</t>
@@ -756,7 +798,7 @@
     <t xml:space="preserve">Holzofen-Saunahaus am Steg (15 Plätze)</t>
   </si>
   <si>
-    <t xml:space="preserve">Massivholz, holzbefeuert, Funkenschutz</t>
+    <t xml:space="preserve">Massivholz, Pelletofen mit automatischer Beschickung</t>
   </si>
   <si>
     <t xml:space="preserve">Tauchbecken innen</t>
@@ -783,10 +825,10 @@
     <t xml:space="preserve">Hochwertige Relaxliegen</t>
   </si>
   <si>
-    <t xml:space="preserve">Gastro-Küche &amp; Theke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Regenerierküche, Kühlung, Kaffeetechnik</t>
+    <t xml:space="preserve">Gastro: Smart-Fridges, Automaten, Theke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Smart-Fridges mit Armband-Zahlung, Kaffeevollautomat, Getränkekühlung, Sitzbereich</t>
   </si>
   <si>
     <t xml:space="preserve">Möblierung, Deko, Leitsystem</t>
@@ -795,7 +837,7 @@
     <t xml:space="preserve">Kassen-/Zutrittssystem, Spinde, IT</t>
   </si>
   <si>
-    <t xml:space="preserve">Chip-Armband, Online-Ticketing</t>
+    <t xml:space="preserve">Online-Ticketing, 2 Kiosk-Terminals, Drehkreuze, RFID-Armband, Kameras Steg/Außenbereich</t>
   </si>
   <si>
     <t xml:space="preserve">Summe KG 5</t>
@@ -921,7 +963,7 @@
     <t xml:space="preserve">Eintrittserlöse</t>
   </si>
   <si>
-    <t xml:space="preserve">Gastronomie (Bistro)</t>
+    <t xml:space="preserve">Gastronomie (Smart-Fridge, Automaten)</t>
   </si>
   <si>
     <t xml:space="preserve">Strandbad-Kiosk (Sommer)</t>
@@ -963,6 +1005,9 @@
     <t xml:space="preserve">Wäsche, Reinigung, Verbrauchsmaterial</t>
   </si>
   <si>
+    <t xml:space="preserve">Fremdleistungen (Reinigung, Event-Aufgüsse, Technik, Lizenzen)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Marketing</t>
   </si>
   <si>
@@ -990,7 +1035,7 @@
     <t xml:space="preserve">Pachtquote</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixkosten (Personal, Energie, Wasser, Verwaltung)</t>
+    <t xml:space="preserve">Fixkosten (Personal, Fremdleistungen, Energie, Wasser, Verwaltung)</t>
   </si>
   <si>
     <t xml:space="preserve">Deckungsbeitrag je Besuch (nach Umsatzpacht)</t>
@@ -1002,19 +1047,28 @@
     <t xml:space="preserve">Break-even in % der geplanten Besuche</t>
   </si>
   <si>
-    <t xml:space="preserve">Stellenbesetzungsplan Betreiber (Normaljahr, Gehälter = Annahmen)</t>
+    <t xml:space="preserve">Stellenbesetzungsplan Betreiber – schlankes Host-Modell (Normaljahr, Gehälter = Annahmen)</t>
   </si>
   <si>
     <t xml:space="preserve">Gehälter orientiert am KV Hotel- und Gastgewerbe (Arbeiter/Angestellte) mit marktüblicher Überzahlung im Salzkammergut – vor Verwendung mit dem aktuell gültigen KV abgleichen.</t>
   </si>
   <si>
-    <t xml:space="preserve">Öffnungsstunden pro Tag (10–22 Uhr)</t>
+    <t xml:space="preserve">Tage mit 12 h Öffnung (10–22 Uhr: Fr–So, Ferien)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~14 Ferienwochen täglich + übrige Wochen Fr–So</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tage mit 8 h Öffnung (14–22 Uhr: Mo–Do außerhalb Ferien)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rest der Betriebstage</t>
   </si>
   <si>
     <t xml:space="preserve">Vor-/Nachbereitung pro Tag (h)</t>
   </si>
   <si>
-    <t xml:space="preserve">Aufheizen, Reinigung, Kassenabschluss</t>
+    <t xml:space="preserve">Aufheizen, Kontrollgang, Abschluss</t>
   </si>
   <si>
     <t xml:space="preserve">Betriebstage pro Jahr</t>
@@ -1023,7 +1077,25 @@
     <t xml:space="preserve">aus Annahmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Betriebsstunden pro Jahr</t>
+    <t xml:space="preserve">Betriebsstunden pro Jahr (je Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mindestbesetzung (Personen, immer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Keine Alleinarbeit; beide mit Erste-Hilfe-/Rettungsschein</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zusatzperson Empfang an 12-h-Tagen (h/Tag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hybrid-Kassa: besetzter Empfang ca. 15–21 Uhr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bedarf Schichtstunden pro Jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Präsenzstunden im Haus</t>
   </si>
   <si>
     <t xml:space="preserve">Wochenarbeitszeit (h)</t>
@@ -1056,9 +1128,6 @@
     <t xml:space="preserve">VZÄ je durchgehend besetzter Position</t>
   </si>
   <si>
-    <t xml:space="preserve">Faustregel: 1 Dauerposition ≈ 2,7 VZÄ</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gehälter pro Jahr</t>
   </si>
   <si>
@@ -1080,7 +1149,13 @@
     <t xml:space="preserve">Aushilfen / Geringfügige (pauschal, inkl. Abgaben)</t>
   </si>
   <si>
-    <t xml:space="preserve">Spitzen: Wochenende, Events, Sommer-Kiosk</t>
+    <t xml:space="preserve">Ausfälle, Spitzentage, Sommer-Kiosk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Referenz: Personalkosten bisheriges Konzept (20 VZÄ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bistro mit Küche, Personenkassa, eigene Reinigung, volles Aufgussprogramm</t>
   </si>
   <si>
     <t xml:space="preserve">Funktion</t>
@@ -1101,79 +1176,55 @@
     <t xml:space="preserve">Personalkosten (€)</t>
   </si>
   <si>
-    <t xml:space="preserve">Ø Besetzung je Betriebsstunde</t>
+    <t xml:space="preserve">Schichtanteil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Schichtstunden p. a.</t>
   </si>
   <si>
     <t xml:space="preserve">Aufgaben / Einstufung</t>
   </si>
   <si>
-    <t xml:space="preserve">Betriebsleitung</t>
+    <t xml:space="preserve">Betriebsleitung (arbeitet in Schichten mit)</t>
   </si>
   <si>
     <t xml:space="preserve">Leitung</t>
   </si>
   <si>
-    <t xml:space="preserve">Gesamtverantwortung, Personal, Budget, Marketing; Tagdienst + Rufbereitschaft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stv. Leitung / Gästeservice-Leitung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dienstplanung, Kassa/Rezeption, Hotelkooperationen, Events</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haustechnik / Bademeister:in</t>
+    <t xml:space="preserve">Gesamtverantwortung, Personal, Einkauf, Marketing; ca. 50 % als Host im Dienst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior-Host / Stv. Leitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dienstplan, Aufgussplan, Hotelkooperationen, Events; vertritt die Leitung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Host:innen Sauna &amp; Aufsicht</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sauna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4–5 Aufgüsse/Tag, Aufsicht Steg/Becken, Erste Hilfe, Smart-Fridge nachfüllen, Zwischenreinigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Host:in Empfang &amp; Service</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gästeservice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Besetzter Empfang zu Spitzenzeiten, Hilfe am Kiosk-Terminal, Gutscheine, Telefon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haustechnik / Hausmeister:in (geteilt mit Strandbad)</t>
   </si>
   <si>
     <t xml:space="preserve">Technik</t>
   </si>
   <si>
-    <t xml:space="preserve">Wärmepumpe, Wasseraufbereitung, Saunaöfen, Holzofen; Bäderhygiene</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saunameister:in – Teamleitung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sauna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufgussplan, Event-Aufgüsse, Einschulung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saunameister:innen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aufgüsse, Aufsicht Saunabereich &amp; Steg, Erste Hilfe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rezeption / Kassa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gästeservice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check-in, Verkauf, Gutscheine, Telefon/Online</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reinigung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laufende Reinigung Nass-/Ruhebereiche, Wäschelogistik</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Koch / Köchin (Regenerierküche)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gastro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Service / Theke Bistro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Theke, Bademantel-Bistro, im Sommer Kiosk</t>
+    <t xml:space="preserve">Kontrollgänge, Wasserwerte, Kleinreparaturen; Rest über Wartungsvertrag</t>
   </si>
   <si>
     <t xml:space="preserve">Summe Stammpersonal</t>
@@ -1191,7 +1242,19 @@
     <t xml:space="preserve">Personalkosten in % vom Umsatz (aktives Szenario)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lesart Spalte I: Wie viele Personen dieser Funktion im Schnitt je Betriebsstunde im Haus sind. Summe ≈ 7–8 Personen gleichzeitig; Leitung/Technik arbeiten überwiegend im Tagdienst.</t>
+    <t xml:space="preserve">Deckung Schichtbedarf (verfügbare / benötigte Stunden)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einsparung Personal ggü. bisherigem Konzept</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abzgl. neue Fremdleistungen (Reinigung, Event-Aufgüsse, Technik, Lizenzen)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netto-Einsparung Kostenseite (Basis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Host-Prinzip: immer 2 Personen im Haus (keine Alleinarbeit), an 12-h-Tagen nachmittags/abends eine 3. am Empfang. Zutritt über Online-Ticket, Kiosk und Drehkreuz; Gastro als Smart-Fridge; Grundreinigung nachts durch Fremdfirma; Massage über freie Masseur:innen (Provision).</t>
   </si>
   <si>
     <t xml:space="preserve">Betreiber-GuV &amp; Pachtfluss – 10 Jahre (aktives Szenario, nominal)</t>
@@ -1528,7 +1591,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1617,14 +1680,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1638,6 +1693,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1678,10 +1737,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="170" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1992,15 +2047,15 @@
       </c>
       <c r="C4" s="4" t="n">
         <f aca="false">Umsatz!C6</f>
-        <v>36000</v>
+        <v>34200</v>
       </c>
       <c r="D4" s="4" t="n">
         <f aca="false">Umsatz!D6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="E4" s="4" t="n">
         <f aca="false">Umsatz!E6</f>
-        <v>57215</v>
+        <v>56070.7</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2032,15 +2087,15 @@
       </c>
       <c r="C6" s="4" t="n">
         <f aca="false">Umsatz!C16</f>
-        <v>1315174.15352059</v>
+        <v>1153047.23932282</v>
       </c>
       <c r="D6" s="4" t="n">
         <f aca="false">Umsatz!D16</f>
-        <v>1934607.64755675</v>
+        <v>1744137.98334744</v>
       </c>
       <c r="E6" s="4" t="n">
         <f aca="false">Umsatz!E16</f>
-        <v>2593479.21796845</v>
+        <v>2376772.17708734</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2052,15 +2107,15 @@
       </c>
       <c r="C7" s="5" t="n">
         <f aca="false">Umsatz!C17</f>
-        <v>36.5326153755718</v>
+        <v>33.7148315591467</v>
       </c>
       <c r="D7" s="5" t="n">
         <f aca="false">Umsatz!D17</f>
-        <v>41.0570383607121</v>
+        <v>38.1596009168834</v>
       </c>
       <c r="E7" s="5" t="n">
         <f aca="false">Umsatz!E17</f>
-        <v>45.3286588826086</v>
+        <v>42.3888443890899</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2071,16 +2126,16 @@
         <v>11</v>
       </c>
       <c r="C8" s="4" t="n">
-        <f aca="false">Betriebskosten!C13</f>
-        <v>1662815.55855906</v>
+        <f aca="false">Betriebskosten!C14</f>
+        <v>1216869.6472593</v>
       </c>
       <c r="D8" s="4" t="n">
-        <f aca="false">Betriebskosten!D13</f>
-        <v>1695030.21102732</v>
+        <f aca="false">Betriebskosten!D14</f>
+        <v>1233413.12439215</v>
       </c>
       <c r="E8" s="4" t="n">
-        <f aca="false">Betriebskosten!E13</f>
-        <v>1801765.59220854</v>
+        <f aca="false">Betriebskosten!E14</f>
+        <v>1392166.80970737</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2091,16 +2146,16 @@
         <v>11</v>
       </c>
       <c r="C9" s="4" t="n">
-        <f aca="false">Betriebskosten!C15</f>
+        <f aca="false">Betriebskosten!C16</f>
         <v>150000</v>
       </c>
       <c r="D9" s="4" t="n">
-        <f aca="false">Betriebskosten!D15</f>
-        <v>193460.764755675</v>
+        <f aca="false">Betriebskosten!D16</f>
+        <v>174413.798334744</v>
       </c>
       <c r="E9" s="4" t="n">
-        <f aca="false">Betriebskosten!E15</f>
-        <v>259347.921796845</v>
+        <f aca="false">Betriebskosten!E16</f>
+        <v>237677.217708734</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2111,16 +2166,16 @@
         <v>11</v>
       </c>
       <c r="C10" s="4" t="n">
-        <f aca="false">Betriebskosten!C16</f>
-        <v>-497641.405038476</v>
+        <f aca="false">Betriebskosten!C17</f>
+        <v>-213822.407936484</v>
       </c>
       <c r="D10" s="4" t="n">
-        <f aca="false">Betriebskosten!D16</f>
-        <v>46116.6717737592</v>
+        <f aca="false">Betriebskosten!D17</f>
+        <v>336311.060620546</v>
       </c>
       <c r="E10" s="4" t="n">
-        <f aca="false">Betriebskosten!E16</f>
-        <v>532365.703963063</v>
+        <f aca="false">Betriebskosten!E17</f>
+        <v>746928.149671241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2131,16 +2186,16 @@
         <v>17</v>
       </c>
       <c r="C11" s="6" t="n">
-        <f aca="false">Betriebskosten!C18</f>
-        <v>-0.378384416775787</v>
+        <f aca="false">Betriebskosten!C19</f>
+        <v>-0.185441151623641</v>
       </c>
       <c r="D11" s="6" t="n">
-        <f aca="false">Betriebskosten!D18</f>
-        <v>0.0238377387952543</v>
+        <f aca="false">Betriebskosten!D19</f>
+        <v>0.192823654912371</v>
       </c>
       <c r="E11" s="6" t="n">
-        <f aca="false">Betriebskosten!E18</f>
-        <v>0.205270857878738</v>
+        <f aca="false">Betriebskosten!E19</f>
+        <v>0.314261567377727</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,16 +2206,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="4" t="n">
-        <f aca="false">Betriebskosten!C24</f>
-        <v>55222.8469556743</v>
+        <f aca="false">Betriebskosten!C25</f>
+        <v>42105.215813122</v>
       </c>
       <c r="D12" s="4" t="n">
-        <f aca="false">Betriebskosten!D24</f>
-        <v>45490.4536776339</v>
+        <f aca="false">Betriebskosten!D25</f>
+        <v>32674.7420243392</v>
       </c>
       <c r="E12" s="4" t="n">
-        <f aca="false">Betriebskosten!E24</f>
-        <v>40290.9061930512</v>
+        <f aca="false">Betriebskosten!E25</f>
+        <v>30102.2377174364</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2171,16 +2226,16 @@
         <v>17</v>
       </c>
       <c r="C13" s="6" t="n">
-        <f aca="false">Betriebskosten!C25</f>
-        <v>1.53396797099095</v>
+        <f aca="false">Betriebskosten!C26</f>
+        <v>1.2311466612024</v>
       </c>
       <c r="D13" s="6" t="n">
-        <f aca="false">Betriebskosten!D25</f>
-        <v>0.965417098421772</v>
+        <f aca="false">Betriebskosten!D26</f>
+        <v>0.714883299151524</v>
       </c>
       <c r="E13" s="6" t="n">
-        <f aca="false">Betriebskosten!E25</f>
-        <v>0.704201803601349</v>
+        <f aca="false">Betriebskosten!E26</f>
+        <v>0.536862170749365</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2191,16 +2246,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">Betriebskosten!C15-Investition!$F$49*Annahmen!$C$45-Annahmen!$C$46</f>
-        <v>70096</v>
+        <f aca="false">Betriebskosten!C16-Investition!$F$49*Annahmen!$C$50-Annahmen!$C$51</f>
+        <v>69976</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">Betriebskosten!D15-Investition!$F$49*Annahmen!$D$45-Annahmen!$D$46</f>
-        <v>113556.764755675</v>
+        <f aca="false">Betriebskosten!D16-Investition!$F$49*Annahmen!$D$50-Annahmen!$D$51</f>
+        <v>94389.7983347442</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">Betriebskosten!E15-Investition!$F$49*Annahmen!$E$45-Annahmen!$E$46</f>
-        <v>179443.921796845</v>
+        <f aca="false">Betriebskosten!E16-Investition!$F$49*Annahmen!$E$50-Annahmen!$E$51</f>
+        <v>157653.217708734</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2212,15 +2267,15 @@
       </c>
       <c r="C15" s="4" t="n">
         <f aca="false">Investition!$F$58</f>
-        <v>8557224.8</v>
+        <v>8541365.6</v>
       </c>
       <c r="D15" s="4" t="n">
         <f aca="false">Investition!$F$58</f>
-        <v>8557224.8</v>
+        <v>8541365.6</v>
       </c>
       <c r="E15" s="4" t="n">
         <f aca="false">Investition!$F$58</f>
-        <v>8557224.8</v>
+        <v>8541365.6</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2232,15 +2287,15 @@
       </c>
       <c r="C16" s="8" t="n">
         <f aca="false">IF(C14&gt;0,Investition!$F$58/C14,"n/a")</f>
-        <v>122.078646427756</v>
+        <v>122.061358179947</v>
       </c>
       <c r="D16" s="8" t="n">
         <f aca="false">IF(D14&gt;0,Investition!$F$58/D14,"n/a")</f>
-        <v>75.3563631229845</v>
+        <v>90.4903469515729</v>
       </c>
       <c r="E16" s="8" t="n">
         <f aca="false">IF(E14&gt;0,Investition!$F$58/E14,"n/a")</f>
-        <v>47.68745976076</v>
+        <v>54.17818756976</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2251,16 +2306,16 @@
         <v>17</v>
       </c>
       <c r="C17" s="9" t="n">
-        <f aca="false">MAX(0,Betriebskosten!C14/Umsatz!C16-Annahmen!$C$43)</f>
+        <f aca="false">MAX(0,Betriebskosten!C15/Umsatz!C16-Annahmen!$C$48)</f>
         <v>0</v>
       </c>
       <c r="D17" s="9" t="n">
-        <f aca="false">MAX(0,Betriebskosten!D14/Umsatz!D16-Annahmen!$D$43)</f>
-        <v>0.0438377387952543</v>
+        <f aca="false">MAX(0,Betriebskosten!D15/Umsatz!D16-Annahmen!$D$48)</f>
+        <v>0.212823654912371</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">MAX(0,Betriebskosten!E14/Umsatz!E16-Annahmen!$E$43)</f>
-        <v>0.225270857878738</v>
+        <f aca="false">MAX(0,Betriebskosten!E15/Umsatz!E16-Annahmen!$E$48)</f>
+        <v>0.334261567377727</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2276,11 +2331,11 @@
       </c>
       <c r="D18" s="4" t="n">
         <f aca="false">D17*Umsatz!D16</f>
-        <v>84808.8247248943</v>
+        <v>371193.820287495</v>
       </c>
       <c r="E18" s="4" t="n">
         <f aca="false">E17*Umsatz!E16</f>
-        <v>584235.288322432</v>
+        <v>794463.593212988</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2311,7 +2366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14"/>
@@ -2523,34 +2578,34 @@
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="15" t="s">
         <v>51</v>
       </c>
+      <c r="B13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <f aca="false">INDEX(C13:E13,1,$C$4)</f>
+        <v>0.03</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>36</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>39</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>42</v>
-      </c>
-      <c r="F14" s="17" t="n">
-        <f aca="false">INDEX(C14:E14,1,$C$4)</f>
-        <v>39</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H14" s="18" t="s">
+      <c r="B14" s="12" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2561,18 +2616,18 @@
       <c r="B15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C15" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>27</v>
+      <c r="C15" s="19" t="n">
+        <v>36</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>39</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>42</v>
       </c>
       <c r="F15" s="17" t="n">
         <f aca="false">INDEX(C15:E15,1,$C$4)</f>
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>11</v>
@@ -2588,53 +2643,53 @@
       <c r="B16" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="9" t="n">
-        <f aca="false">D16</f>
-        <v>0.55</v>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E16" s="9" t="n">
-        <f aca="false">D16</f>
-        <v>0.55</v>
-      </c>
-      <c r="F16" s="21" t="n">
+      <c r="C16" s="16" t="n">
+        <v>23</v>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>27</v>
+      </c>
+      <c r="F16" s="17" t="n">
         <f aca="false">INDEX(C16:E16,1,$C$4)</f>
-        <v>0.55</v>
+        <v>25</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H16" s="18" t="s">
-        <v>31</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="20" t="n">
-        <v>0.15</v>
+        <v>62</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <f aca="false">D17</f>
+        <v>0.55</v>
       </c>
       <c r="D17" s="20" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="E17" s="20" t="n">
-        <v>0.1</v>
+        <v>0.55</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">D17</f>
+        <v>0.55</v>
       </c>
       <c r="F17" s="21" t="n">
         <f aca="false">INDEX(C17:E17,1,$C$4)</f>
-        <v>0.12</v>
+        <v>0.55</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="18" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2644,20 +2699,18 @@
       <c r="B18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C18" s="9" t="n">
-        <f aca="false">D18</f>
-        <v>0.13</v>
+      <c r="C18" s="20" t="n">
+        <v>0.15</v>
       </c>
       <c r="D18" s="20" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <f aca="false">D18</f>
-        <v>0.13</v>
+        <v>0.12</v>
+      </c>
+      <c r="E18" s="20" t="n">
+        <v>0.1</v>
       </c>
       <c r="F18" s="21" t="n">
         <f aca="false">INDEX(C18:E18,1,$C$4)</f>
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>17</v>
@@ -2667,34 +2720,36 @@
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="15" t="s">
         <v>66</v>
       </c>
+      <c r="B19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <f aca="false">D19</f>
+        <v>0.13</v>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <f aca="false">D19</f>
+        <v>0.13</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <f aca="false">INDEX(C19:E19,1,$C$4)</f>
+        <v>0.13</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="18" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="D20" s="22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <f aca="false">INDEX(C20:E20,1,$C$4)</f>
-        <v>12.5</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H20" s="18" t="s">
+      <c r="B20" s="12" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2705,23 +2760,21 @@
       <c r="B21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="9" t="n">
-        <f aca="false">D21</f>
-        <v>0.15</v>
-      </c>
-      <c r="D21" s="20" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E21" s="9" t="n">
-        <f aca="false">D21</f>
-        <v>0.15</v>
-      </c>
-      <c r="F21" s="21" t="n">
+      <c r="C21" s="19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D21" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="E21" s="19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="F21" s="17" t="n">
         <f aca="false">INDEX(C21:E21,1,$C$4)</f>
-        <v>0.15</v>
+        <v>9</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H21" s="18" t="s">
         <v>72</v>
@@ -2736,18 +2789,18 @@
       </c>
       <c r="C22" s="9" t="n">
         <f aca="false">D22</f>
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="D22" s="20" t="n">
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="E22" s="9" t="n">
         <f aca="false">D22</f>
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="F22" s="21" t="n">
         <f aca="false">INDEX(C22:E22,1,$C$4)</f>
-        <v>0.32</v>
+        <v>0.15</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>17</v>
@@ -2763,138 +2816,138 @@
       <c r="B23" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="16" t="n">
-        <v>45000</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E23" s="16" t="n">
-        <v>75000</v>
-      </c>
-      <c r="F23" s="17" t="n">
+      <c r="C23" s="9" t="n">
+        <f aca="false">D23</f>
+        <v>0.45</v>
+      </c>
+      <c r="D23" s="20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <f aca="false">D23</f>
+        <v>0.45</v>
+      </c>
+      <c r="F23" s="21" t="n">
         <f aca="false">INDEX(C23:E23,1,$C$4)</f>
-        <v>60000</v>
+        <v>0.45</v>
       </c>
       <c r="G23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="18" t="s">
         <v>78</v>
-      </c>
-      <c r="H23" s="18" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="16" t="n">
+        <v>45000</v>
+      </c>
+      <c r="D24" s="16" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E24" s="16" t="n">
+        <v>75000</v>
+      </c>
+      <c r="F24" s="17" t="n">
+        <f aca="false">INDEX(C24:E24,1,$C$4)</f>
+        <v>60000</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="9" t="n">
-        <f aca="false">D24</f>
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="20" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E24" s="9" t="n">
-        <f aca="false">D24</f>
-        <v>0.4</v>
-      </c>
-      <c r="F24" s="21" t="n">
-        <f aca="false">INDEX(C24:E24,1,$C$4)</f>
-        <v>0.4</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="H24" s="18" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="16" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D25" s="16" t="n">
-        <v>4000</v>
-      </c>
-      <c r="E25" s="16" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F25" s="17" t="n">
+        <v>84</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <f aca="false">D25</f>
+        <v>0.4</v>
+      </c>
+      <c r="D25" s="20" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <f aca="false">D25</f>
+        <v>0.4</v>
+      </c>
+      <c r="F25" s="21" t="n">
         <f aca="false">INDEX(C25:E25,1,$C$4)</f>
-        <v>4000</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="H25" s="18" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <f aca="false">D26</f>
-        <v>75</v>
+      <c r="C26" s="16" t="n">
+        <v>3000</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>75</v>
-      </c>
-      <c r="E26" s="7" t="n">
-        <f aca="false">D26</f>
-        <v>75</v>
+        <v>4000</v>
+      </c>
+      <c r="E26" s="16" t="n">
+        <v>5000</v>
       </c>
       <c r="F26" s="17" t="n">
         <f aca="false">INDEX(C26:E26,1,$C$4)</f>
-        <v>75</v>
+        <v>4000</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="H26" s="18" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C27" s="9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C27" s="7" t="n">
         <f aca="false">D27</f>
-        <v>0.2</v>
-      </c>
-      <c r="D27" s="20" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E27" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="D27" s="16" t="n">
+        <v>75</v>
+      </c>
+      <c r="E27" s="7" t="n">
         <f aca="false">D27</f>
-        <v>0.2</v>
-      </c>
-      <c r="F27" s="21" t="n">
+        <v>75</v>
+      </c>
+      <c r="F27" s="17" t="n">
         <f aca="false">INDEX(C27:E27,1,$C$4)</f>
-        <v>0.2</v>
+        <v>75</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H27" s="18" t="s">
-        <v>90</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2906,18 +2959,18 @@
       </c>
       <c r="C28" s="9" t="n">
         <f aca="false">D28</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="D28" s="20" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="E28" s="9" t="n">
         <f aca="false">D28</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="F28" s="21" t="n">
         <f aca="false">INDEX(C28:E28,1,$C$4)</f>
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>17</v>
@@ -2933,21 +2986,23 @@
       <c r="B29" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C29" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>55</v>
-      </c>
-      <c r="F29" s="17" t="n">
+      <c r="C29" s="9" t="n">
+        <f aca="false">D29</f>
+        <v>0.25</v>
+      </c>
+      <c r="D29" s="20" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E29" s="9" t="n">
+        <f aca="false">D29</f>
+        <v>0.25</v>
+      </c>
+      <c r="F29" s="21" t="n">
         <f aca="false">INDEX(C29:E29,1,$C$4)</f>
-        <v>40</v>
+        <v>0.25</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>84</v>
+        <v>17</v>
       </c>
       <c r="H29" s="18" t="s">
         <v>96</v>
@@ -2960,87 +3015,84 @@
       <c r="B30" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="7" t="n">
-        <f aca="false">D30</f>
-        <v>2500</v>
+      <c r="C30" s="16" t="n">
+        <v>25</v>
       </c>
       <c r="D30" s="16" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E30" s="7" t="n">
-        <f aca="false">D30</f>
-        <v>2500</v>
+        <v>40</v>
+      </c>
+      <c r="E30" s="16" t="n">
+        <v>55</v>
       </c>
       <c r="F30" s="17" t="n">
         <f aca="false">INDEX(C30:E30,1,$C$4)</f>
+        <v>40</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H30" s="18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C31" s="7" t="n">
+        <f aca="false">D31</f>
         <v>2500</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="D31" s="16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <f aca="false">D31</f>
+        <v>2500</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <f aca="false">INDEX(C31:E31,1,$C$4)</f>
+        <v>2500</v>
+      </c>
+      <c r="G31" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="H30" s="18" t="s">
+      <c r="H31" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="12" t="s">
-        <v>99</v>
-      </c>
-    </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C32" s="24" t="n">
-        <f aca="false">D32+1</f>
-        <v>21</v>
-      </c>
-      <c r="D32" s="25" t="n">
-        <f aca="false">Stellenplan!C29</f>
-        <v>20</v>
-      </c>
-      <c r="E32" s="19" t="n">
-        <v>20</v>
-      </c>
-      <c r="F32" s="17" t="n">
-        <f aca="false">INDEX(C32:E32,1,$C$4)</f>
-        <v>20</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="B32" s="12" t="s">
         <v>102</v>
-      </c>
-      <c r="H32" s="18" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <f aca="false">D33</f>
-        <v>49119.705</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <f aca="false">Stellenplan!H32</f>
-        <v>49119.705</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <f aca="false">D33</f>
-        <v>49119.705</v>
+      <c r="C33" s="22" t="n">
+        <f aca="false">D33+1</f>
+        <v>7.3</v>
+      </c>
+      <c r="D33" s="23" t="n">
+        <f aca="false">Stellenplan!C30</f>
+        <v>6.3</v>
+      </c>
+      <c r="E33" s="19" t="n">
+        <v>7</v>
       </c>
       <c r="F33" s="17" t="n">
         <f aca="false">INDEX(C33:E33,1,$C$4)</f>
-        <v>49119.705</v>
+        <v>6.3</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>78</v>
+        <v>105</v>
       </c>
       <c r="H33" s="18" t="s">
         <v>106</v>
@@ -3053,21 +3105,24 @@
       <c r="B34" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C34" s="19" t="n">
-        <v>220000</v>
-      </c>
-      <c r="D34" s="19" t="n">
-        <v>180000</v>
-      </c>
-      <c r="E34" s="19" t="n">
-        <v>160000</v>
+      <c r="C34" s="7" t="n">
+        <f aca="false">D34</f>
+        <v>60832.4996825397</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <f aca="false">Stellenplan!H33</f>
+        <v>60832.4996825397</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <f aca="false">D34</f>
+        <v>60832.4996825397</v>
       </c>
       <c r="F34" s="17" t="n">
         <f aca="false">INDEX(C34:E34,1,$C$4)</f>
-        <v>180000</v>
+        <v>60832.4996825397</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H34" s="18" t="s">
         <v>109</v>
@@ -3080,52 +3135,50 @@
       <c r="B35" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C35" s="7" t="n">
-        <f aca="false">D35</f>
-        <v>40000</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E35" s="7" t="n">
-        <f aca="false">D35</f>
-        <v>40000</v>
+      <c r="C35" s="19" t="n">
+        <v>220000</v>
+      </c>
+      <c r="D35" s="19" t="n">
+        <v>180000</v>
+      </c>
+      <c r="E35" s="19" t="n">
+        <v>160000</v>
       </c>
       <c r="F35" s="17" t="n">
         <f aca="false">INDEX(C35:E35,1,$C$4)</f>
-        <v>40000</v>
+        <v>180000</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H35" s="18" t="s">
-        <v>31</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="15" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C36" s="26" t="n">
+        <v>114</v>
+      </c>
+      <c r="C36" s="7" t="n">
         <f aca="false">D36</f>
-        <v>2.2</v>
-      </c>
-      <c r="D36" s="27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="E36" s="26" t="n">
+        <v>40000</v>
+      </c>
+      <c r="D36" s="16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E36" s="7" t="n">
         <f aca="false">D36</f>
-        <v>2.2</v>
-      </c>
-      <c r="F36" s="23" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F36" s="17" t="n">
         <f aca="false">INDEX(C36:E36,1,$C$4)</f>
-        <v>2.2</v>
+        <v>40000</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>11</v>
+        <v>81</v>
       </c>
       <c r="H36" s="18" t="s">
         <v>31</v>
@@ -3133,28 +3186,28 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="9" t="n">
+        <v>116</v>
+      </c>
+      <c r="C37" s="24" t="n">
         <f aca="false">D37</f>
-        <v>0.04</v>
-      </c>
-      <c r="D37" s="20" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="E37" s="9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="D37" s="25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E37" s="24" t="n">
         <f aca="false">D37</f>
-        <v>0.04</v>
-      </c>
-      <c r="F37" s="21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F37" s="26" t="n">
         <f aca="false">INDEX(C37:E37,1,$C$4)</f>
-        <v>0.04</v>
+        <v>2.2</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H37" s="18" t="s">
         <v>31</v>
@@ -3162,31 +3215,31 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="15" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C38" s="9" t="n">
         <f aca="false">D38</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D38" s="20" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="E38" s="9" t="n">
         <f aca="false">D38</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F38" s="21" t="n">
         <f aca="false">INDEX(C38:E38,1,$C$4)</f>
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H38" s="18" t="s">
-        <v>118</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3196,270 +3249,292 @@
       <c r="B39" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C39" s="7" t="n">
+      <c r="C39" s="9" t="n">
         <f aca="false">D39</f>
+        <v>0.02</v>
+      </c>
+      <c r="D39" s="20" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E39" s="9" t="n">
+        <f aca="false">D39</f>
+        <v>0.02</v>
+      </c>
+      <c r="F39" s="21" t="n">
+        <f aca="false">INDEX(C39:E39,1,$C$4)</f>
+        <v>0.02</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="18" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <f aca="false">D40</f>
         <v>85000</v>
       </c>
-      <c r="D39" s="16" t="n">
+      <c r="D40" s="16" t="n">
         <v>85000</v>
       </c>
-      <c r="E39" s="7" t="n">
-        <f aca="false">D39</f>
+      <c r="E40" s="7" t="n">
+        <f aca="false">D40</f>
         <v>85000</v>
       </c>
-      <c r="F39" s="17" t="n">
-        <f aca="false">INDEX(C39:E39,1,$C$4)</f>
+      <c r="F40" s="17" t="n">
+        <f aca="false">INDEX(C40:E40,1,$C$4)</f>
         <v>85000</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H39" s="18" t="s">
+      <c r="G40" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H40" s="18" t="s">
         <v>31</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="12" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="15" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C41" s="28" t="n">
-        <f aca="false">D41</f>
-        <v>0.1</v>
-      </c>
-      <c r="D41" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E41" s="28" t="n">
-        <f aca="false">D41</f>
-        <v>0.1</v>
-      </c>
-      <c r="F41" s="21" t="n">
+        <v>125</v>
+      </c>
+      <c r="C41" s="16" t="n">
+        <v>100000</v>
+      </c>
+      <c r="D41" s="16" t="n">
+        <v>90000</v>
+      </c>
+      <c r="E41" s="16" t="n">
+        <v>90000</v>
+      </c>
+      <c r="F41" s="17" t="n">
         <f aca="false">INDEX(C41:E41,1,$C$4)</f>
-        <v>0.1</v>
+        <v>90000</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H41" s="18" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C42" s="7" t="n">
         <f aca="false">D42</f>
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="D42" s="16" t="n">
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="E42" s="7" t="n">
         <f aca="false">D42</f>
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="F42" s="17" t="n">
         <f aca="false">INDEX(C42:E42,1,$C$4)</f>
-        <v>150000</v>
+        <v>25000</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H42" s="18" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C43" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="C43" s="7" t="n">
         <f aca="false">D43</f>
-        <v>0.08</v>
-      </c>
-      <c r="D43" s="20" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="E43" s="9" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D43" s="16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E43" s="7" t="n">
         <f aca="false">D43</f>
-        <v>0.08</v>
-      </c>
-      <c r="F43" s="21" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F43" s="17" t="n">
         <f aca="false">INDEX(C43:E43,1,$C$4)</f>
-        <v>0.08</v>
+        <v>20000</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H43" s="18" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="12" t="s">
-        <v>131</v>
+      <c r="A44" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <f aca="false">D44</f>
+        <v>20000</v>
+      </c>
+      <c r="D44" s="16" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <f aca="false">D44</f>
+        <v>20000</v>
+      </c>
+      <c r="F44" s="17" t="n">
+        <f aca="false">INDEX(C44:E44,1,$C$4)</f>
+        <v>20000</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="H44" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="C45" s="9" t="n">
-        <f aca="false">D45</f>
-        <v>0.008</v>
-      </c>
-      <c r="D45" s="20" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <f aca="false">D45</f>
-        <v>0.008</v>
-      </c>
-      <c r="F45" s="21" t="n">
-        <f aca="false">INDEX(C45:E45,1,$C$4)</f>
-        <v>0.008</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H45" s="18" t="s">
-        <v>134</v>
+      <c r="B45" s="12" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C46" s="7" t="n">
+        <v>137</v>
+      </c>
+      <c r="C46" s="27" t="n">
         <f aca="false">D46</f>
-        <v>25000</v>
-      </c>
-      <c r="D46" s="16" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E46" s="7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D46" s="28" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E46" s="27" t="n">
         <f aca="false">D46</f>
-        <v>25000</v>
-      </c>
-      <c r="F46" s="17" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F46" s="21" t="n">
         <f aca="false">INDEX(C46:E46,1,$C$4)</f>
-        <v>25000</v>
+        <v>0.1</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>78</v>
+        <v>17</v>
       </c>
       <c r="H46" s="18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="C47" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="C47" s="7" t="n">
         <f aca="false">D47</f>
-        <v>0.03</v>
-      </c>
-      <c r="D47" s="20" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E47" s="9" t="n">
+        <v>150000</v>
+      </c>
+      <c r="D47" s="16" t="n">
+        <v>150000</v>
+      </c>
+      <c r="E47" s="7" t="n">
         <f aca="false">D47</f>
-        <v>0.03</v>
-      </c>
-      <c r="F47" s="21" t="n">
+        <v>150000</v>
+      </c>
+      <c r="F47" s="17" t="n">
         <f aca="false">INDEX(C47:E47,1,$C$4)</f>
-        <v>0.03</v>
+        <v>150000</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H47" s="18" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C48" s="9" t="n">
         <f aca="false">D48</f>
-        <v>0.76</v>
+        <v>0.08</v>
       </c>
       <c r="D48" s="20" t="n">
-        <v>0.76</v>
+        <v>0.08</v>
       </c>
       <c r="E48" s="9" t="n">
         <f aca="false">D48</f>
-        <v>0.76</v>
+        <v>0.08</v>
       </c>
       <c r="F48" s="21" t="n">
         <f aca="false">INDEX(C48:E48,1,$C$4)</f>
-        <v>0.76</v>
+        <v>0.08</v>
       </c>
       <c r="G48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H48" s="18" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" s="30" t="n">
+        <v>147</v>
+      </c>
+      <c r="C50" s="9" t="n">
         <f aca="false">D50</f>
-        <v>2029</v>
-      </c>
-      <c r="D50" s="31" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E50" s="30" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="D50" s="20" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="E50" s="9" t="n">
         <f aca="false">D50</f>
-        <v>2029</v>
-      </c>
-      <c r="F50" s="32" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F50" s="21" t="n">
         <f aca="false">INDEX(C50:E50,1,$C$4)</f>
-        <v>2029</v>
+        <v>0.008</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="H50" s="18" t="s">
         <v>148</v>
@@ -3472,108 +3547,229 @@
       <c r="B51" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="C51" s="20" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D51" s="20" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="E51" s="20" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="F51" s="21" t="n">
+      <c r="C51" s="7" t="n">
+        <f aca="false">D51</f>
+        <v>25000</v>
+      </c>
+      <c r="D51" s="16" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="7" t="n">
+        <f aca="false">D51</f>
+        <v>25000</v>
+      </c>
+      <c r="F51" s="17" t="n">
         <f aca="false">INDEX(C51:E51,1,$C$4)</f>
-        <v>0.75</v>
+        <v>25000</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>17</v>
+        <v>81</v>
       </c>
       <c r="H51" s="18" t="s">
-        <v>31</v>
+        <v>151</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C52" s="20" t="n">
-        <v>0.85</v>
+        <v>153</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <f aca="false">D52</f>
+        <v>0.03</v>
       </c>
       <c r="D52" s="20" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E52" s="20" t="n">
-        <v>0.95</v>
+        <v>0.03</v>
+      </c>
+      <c r="E52" s="9" t="n">
+        <f aca="false">D52</f>
+        <v>0.03</v>
       </c>
       <c r="F52" s="21" t="n">
         <f aca="false">INDEX(C52:E52,1,$C$4)</f>
-        <v>0.9</v>
+        <v>0.03</v>
       </c>
       <c r="G52" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H52" s="18" t="s">
-        <v>31</v>
+        <v>154</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C53" s="9" t="n">
         <f aca="false">D53</f>
-        <v>0.025</v>
+        <v>0.76</v>
       </c>
       <c r="D53" s="20" t="n">
-        <v>0.025</v>
+        <v>0.76</v>
       </c>
       <c r="E53" s="9" t="n">
         <f aca="false">D53</f>
-        <v>0.025</v>
+        <v>0.76</v>
       </c>
       <c r="F53" s="21" t="n">
         <f aca="false">INDEX(C53:E53,1,$C$4)</f>
-        <v>0.025</v>
+        <v>0.76</v>
       </c>
       <c r="G53" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H53" s="18" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="12" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C55" s="29" t="n">
+        <f aca="false">D55</f>
+        <v>2029</v>
+      </c>
+      <c r="D55" s="30" t="n">
+        <v>2029</v>
+      </c>
+      <c r="E55" s="29" t="n">
+        <f aca="false">D55</f>
+        <v>2029</v>
+      </c>
+      <c r="F55" s="31" t="n">
+        <f aca="false">INDEX(C55:E55,1,$C$4)</f>
+        <v>2029</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="H55" s="18" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" s="20" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="D56" s="20" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E56" s="20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="F56" s="21" t="n">
+        <f aca="false">INDEX(C56:E56,1,$C$4)</f>
+        <v>0.75</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H56" s="18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C54" s="9" t="n">
-        <f aca="false">D54</f>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C57" s="20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D57" s="20" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E57" s="20" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="F57" s="21" t="n">
+        <f aca="false">INDEX(C57:E57,1,$C$4)</f>
+        <v>0.9</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H57" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="9" t="n">
+        <f aca="false">D58</f>
+        <v>0.025</v>
+      </c>
+      <c r="D58" s="20" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="E58" s="9" t="n">
+        <f aca="false">D58</f>
+        <v>0.025</v>
+      </c>
+      <c r="F58" s="21" t="n">
+        <f aca="false">INDEX(C58:E58,1,$C$4)</f>
+        <v>0.025</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="18" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C59" s="9" t="n">
+        <f aca="false">D59</f>
         <v>0.03</v>
       </c>
-      <c r="D54" s="20" t="n">
+      <c r="D59" s="20" t="n">
         <v>0.03</v>
       </c>
-      <c r="E54" s="9" t="n">
-        <f aca="false">D54</f>
+      <c r="E59" s="9" t="n">
+        <f aca="false">D59</f>
         <v>0.03</v>
       </c>
-      <c r="F54" s="21" t="n">
-        <f aca="false">INDEX(C54:E54,1,$C$4)</f>
+      <c r="F59" s="21" t="n">
+        <f aca="false">INDEX(C59:E59,1,$C$4)</f>
         <v>0.03</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H54" s="18" t="s">
+      <c r="H59" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3607,37 +3803,37 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>160</v>
+        <v>174</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>161</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>162</v>
+        <v>176</v>
       </c>
       <c r="B4" s="16" t="n">
         <v>60</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>163</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>140</v>
@@ -3646,23 +3842,23 @@
         <v>180</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>165</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>100</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>167</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>168</v>
+        <v>182</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>55</v>
@@ -3671,12 +3867,12 @@
         <v>35</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>170</v>
+        <v>184</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>25</v>
@@ -3685,12 +3881,12 @@
         <v>12</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>22</v>
@@ -3699,12 +3895,12 @@
         <v>10</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>30</v>
@@ -3713,23 +3909,23 @@
         <v>15</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>70</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B12" s="16" t="n">
         <v>200</v>
@@ -3738,12 +3934,12 @@
         <v>50</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>200</v>
@@ -3752,12 +3948,12 @@
         <v>50</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="B14" s="16" t="n">
         <v>90</v>
@@ -3766,23 +3962,23 @@
         <v>40</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="B15" s="16" t="n">
         <v>50</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="B16" s="16" t="n">
         <v>40</v>
@@ -3791,12 +3987,12 @@
         <v>2</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="B17" s="16" t="n">
         <v>55</v>
@@ -3805,58 +4001,58 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="B18" s="16" t="n">
         <v>150</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="B19" s="16" t="n">
         <v>140</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="33" t="n">
+        <v>207</v>
+      </c>
+      <c r="B20" s="32" t="n">
         <f aca="false">SUM(B4:B19)</f>
         <v>1427</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="27" t="n">
+        <v>208</v>
+      </c>
+      <c r="B21" s="25" t="n">
         <v>1.18</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="B22" s="33" t="n">
+        <v>210</v>
+      </c>
+      <c r="B22" s="32" t="n">
         <f aca="false">ROUND(B20*B21,-1)</f>
         <v>1680</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="C24" s="7" t="n">
         <f aca="false">C7+C8+C9+C10</f>
@@ -3865,7 +4061,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="C25" s="7" t="n">
         <f aca="false">C12+C13</f>
@@ -3901,50 +4097,50 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>203</v>
+        <v>217</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>205</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>206</v>
+        <v>220</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>208</v>
+        <v>222</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E5" s="16" t="n">
         <v>200000</v>
@@ -3954,18 +4150,18 @@
         <v>200000</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="3" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="C6" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E6" s="16" t="n">
         <v>100000</v>
@@ -3978,9 +4174,9 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" s="33" t="n">
+        <v>226</v>
+      </c>
+      <c r="F7" s="32" t="n">
         <f aca="false">SUM(F5:F6)</f>
         <v>300000</v>
       </c>
@@ -3991,23 +4187,23 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>213</v>
+        <v>227</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>214</v>
+        <v>228</v>
       </c>
       <c r="G9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="3" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="C10" s="4" t="n">
         <f aca="false">Raumprogramm!$B$22</f>
         <v>1680</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E10" s="16" t="n">
         <v>1100</v>
@@ -4017,14 +4213,14 @@
         <v>1848000</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>217</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="F11" s="33" t="n">
+        <v>232</v>
+      </c>
+      <c r="F11" s="32" t="n">
         <f aca="false">SUM(F10:F10)</f>
         <v>1848000</v>
       </c>
@@ -4035,23 +4231,23 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>220</v>
+        <v>234</v>
       </c>
       <c r="G13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="3" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="C14" s="4" t="n">
         <f aca="false">Raumprogramm!$B$22</f>
         <v>1680</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E14" s="16" t="n">
         <v>900</v>
@@ -4061,18 +4257,18 @@
         <v>1512000</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>222</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="C15" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E15" s="16" t="n">
         <v>450000</v>
@@ -4082,18 +4278,18 @@
         <v>450000</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="3" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>150</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
       <c r="E16" s="16" t="n">
         <v>1100</v>
@@ -4103,18 +4299,18 @@
         <v>165000</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>228</v>
+        <v>242</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E17" s="16" t="n">
         <v>120000</v>
@@ -4124,14 +4320,14 @@
         <v>120000</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>229</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="F18" s="33" t="n">
+        <v>244</v>
+      </c>
+      <c r="F18" s="32" t="n">
         <f aca="false">SUM(F14:F17)</f>
         <v>2247000</v>
       </c>
@@ -4142,23 +4338,23 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>231</v>
+        <v>245</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>232</v>
+        <v>246</v>
       </c>
       <c r="G20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>233</v>
+        <v>247</v>
       </c>
       <c r="C21" s="4" t="n">
         <f aca="false">Raumprogramm!$B$22</f>
         <v>1680</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="E21" s="16" t="n">
         <v>1100</v>
@@ -4168,18 +4364,18 @@
         <v>1848000</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>235</v>
+        <v>249</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E22" s="16" t="n">
         <v>260000</v>
@@ -4189,18 +4385,18 @@
         <v>260000</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>237</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>238</v>
+        <v>252</v>
       </c>
       <c r="C23" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E23" s="16" t="n">
         <v>80000</v>
@@ -4213,13 +4409,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="3" t="s">
-        <v>239</v>
+        <v>253</v>
       </c>
       <c r="C24" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E24" s="16" t="n">
         <v>130000</v>
@@ -4229,39 +4425,39 @@
         <v>130000</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="3" t="s">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="C25" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E25" s="16" t="n">
-        <v>220000</v>
+        <v>235000</v>
       </c>
       <c r="F25" s="7" t="n">
         <f aca="false">C25*E25</f>
-        <v>220000</v>
+        <v>235000</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>242</v>
+        <v>256</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="3" t="s">
-        <v>243</v>
+        <v>257</v>
       </c>
       <c r="C26" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E26" s="16" t="n">
         <v>80000</v>
@@ -4274,13 +4470,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="3" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="C27" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E27" s="16" t="n">
         <v>150000</v>
@@ -4290,16 +4486,16 @@
         <v>150000</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="F28" s="33" t="n">
+        <v>260</v>
+      </c>
+      <c r="F28" s="32" t="n">
         <f aca="false">SUM(F21:F27)</f>
-        <v>2768000</v>
+        <v>2783000</v>
       </c>
       <c r="G28" s="18"/>
     </row>
@@ -4308,22 +4504,22 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="G30" s="18"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="3" t="s">
-        <v>249</v>
+        <v>263</v>
       </c>
       <c r="C31" s="16" t="n">
         <v>130</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>236</v>
+        <v>250</v>
       </c>
       <c r="E31" s="16" t="n">
         <v>900</v>
@@ -4333,39 +4529,39 @@
         <v>117000</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>250</v>
+        <v>264</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>251</v>
+        <v>265</v>
       </c>
       <c r="C32" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E32" s="16" t="n">
-        <v>180000</v>
+        <v>90000</v>
       </c>
       <c r="F32" s="7" t="n">
         <f aca="false">C32*E32</f>
-        <v>180000</v>
+        <v>90000</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>252</v>
+        <v>266</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="3" t="s">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="C33" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E33" s="16" t="n">
         <v>200000</v>
@@ -4378,32 +4574,32 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="3" t="s">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="C34" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E34" s="16" t="n">
-        <v>200000</v>
+        <v>260000</v>
       </c>
       <c r="F34" s="7" t="n">
         <f aca="false">C34*E34</f>
-        <v>200000</v>
+        <v>260000</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>255</v>
+        <v>269</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="F35" s="33" t="n">
+        <v>270</v>
+      </c>
+      <c r="F35" s="32" t="n">
         <f aca="false">SUM(F31:F34)</f>
-        <v>697000</v>
+        <v>667000</v>
       </c>
       <c r="G35" s="18"/>
     </row>
@@ -4412,22 +4608,22 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>257</v>
+        <v>271</v>
       </c>
       <c r="B37" s="12" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="G37" s="18"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="3" t="s">
-        <v>259</v>
+        <v>273</v>
       </c>
       <c r="C38" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E38" s="16" t="n">
         <v>300000</v>
@@ -4437,18 +4633,18 @@
         <v>300000</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>260</v>
+        <v>274</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="3" t="s">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="C39" s="16" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>209</v>
+        <v>223</v>
       </c>
       <c r="E39" s="16" t="n">
         <v>250000</v>
@@ -4458,14 +4654,14 @@
         <v>250000</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>262</v>
+        <v>276</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="F40" s="33" t="n">
+        <v>277</v>
+      </c>
+      <c r="F40" s="32" t="n">
         <f aca="false">SUM(F38:F39)</f>
         <v>550000</v>
       </c>
@@ -4476,115 +4672,115 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="F42" s="33" t="n">
+        <v>278</v>
+      </c>
+      <c r="F42" s="32" t="n">
         <f aca="false">F7+F11+F18+F28+F35+F40</f>
-        <v>8410000</v>
+        <v>8395000</v>
       </c>
       <c r="G42" s="18"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>265</v>
+        <v>279</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="E43" s="20" t="n">
         <v>0.15</v>
       </c>
       <c r="F43" s="7" t="n">
         <f aca="false">F42*E43</f>
-        <v>1261500</v>
+        <v>1259250</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="E44" s="20" t="n">
         <v>0.03</v>
       </c>
       <c r="F44" s="7" t="n">
         <f aca="false">F42*E44</f>
-        <v>252300</v>
+        <v>251850</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="E45" s="29" t="n">
+        <v>286</v>
+      </c>
+      <c r="E45" s="28" t="n">
         <v>0.12</v>
       </c>
       <c r="F45" s="7" t="n">
         <f aca="false">(F42+F43+F44)*E45</f>
-        <v>1190856</v>
+        <v>1188732</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="F46" s="34" t="n">
+        <v>288</v>
+      </c>
+      <c r="F46" s="33" t="n">
         <f aca="false">F42+F43+F44+F45</f>
-        <v>11114656</v>
+        <v>11094832</v>
       </c>
       <c r="G46" s="18"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="3" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="F47" s="7" t="n">
         <f aca="false">F46/Raumprogramm!$B$22</f>
-        <v>6615.86666666667</v>
+        <v>6604.06666666667</v>
       </c>
       <c r="G47" s="18"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="3" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="F48" s="7" t="n">
         <f aca="false">F46/120</f>
-        <v>92622.1333333333</v>
+        <v>92456.9333333333</v>
       </c>
       <c r="G48" s="18"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="3" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="F49" s="7" t="n">
         <f aca="false">F11+F18+F28</f>
-        <v>6863000</v>
+        <v>6878000</v>
       </c>
       <c r="G49" s="18"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="3" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="F50" s="7" t="n">
         <f aca="false">F49/Raumprogramm!$B$22</f>
-        <v>4085.11904761905</v>
+        <v>4094.04761904762</v>
       </c>
       <c r="G50" s="18"/>
     </row>
@@ -4593,13 +4789,13 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="12" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="G52" s="18"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="3" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="E53" s="20" t="n">
         <v>0.3</v>
@@ -4609,42 +4805,42 @@
         <v>184500</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="E54" s="29" t="n">
+        <v>296</v>
+      </c>
+      <c r="E54" s="28" t="n">
         <v>0.2</v>
       </c>
       <c r="F54" s="7" t="n">
         <f aca="false">F46*E54</f>
-        <v>2222931.2</v>
+        <v>2218966.4</v>
       </c>
       <c r="G54" s="18" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="3" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="F55" s="16" t="n">
         <v>150000</v>
       </c>
       <c r="G55" s="18" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="12" t="s">
-        <v>286</v>
-      </c>
-      <c r="F56" s="33" t="n">
+        <v>300</v>
+      </c>
+      <c r="F56" s="32" t="n">
         <f aca="false">SUM(F53:F55)</f>
-        <v>2557431.2</v>
+        <v>2553466.4</v>
       </c>
       <c r="G56" s="18"/>
     </row>
@@ -4653,21 +4849,21 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="12" t="s">
-        <v>287</v>
-      </c>
-      <c r="F58" s="34" t="n">
+        <v>301</v>
+      </c>
+      <c r="F58" s="33" t="n">
         <f aca="false">F46-F56</f>
-        <v>8557224.8</v>
+        <v>8541365.6</v>
       </c>
       <c r="G58" s="18"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="3" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F59" s="9" t="n">
         <f aca="false">F56/F46</f>
-        <v>0.230095398364106</v>
+        <v>0.230149172155108</v>
       </c>
       <c r="G59" s="18"/>
     </row>
@@ -4697,12 +4893,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>2</v>
@@ -4722,79 +4918,79 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">Annahmen!$C$8*Annahmen!$C$10</f>
-        <v>28700</v>
+        <f aca="false">Annahmen!$C$8*Annahmen!$C$10*(1-Annahmen!$C$13)</f>
+        <v>27265</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">Annahmen!$D$8*Annahmen!$D$10</f>
-        <v>36900</v>
+        <f aca="false">Annahmen!$D$8*Annahmen!$D$10*(1-Annahmen!$D$13)</f>
+        <v>35793</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">Annahmen!$E$8*Annahmen!$E$10</f>
-        <v>44075</v>
+        <f aca="false">Annahmen!$E$8*Annahmen!$E$10*(1-Annahmen!$E$13)</f>
+        <v>43193.5</v>
       </c>
       <c r="F4" s="7" t="n">
         <f aca="false">INDEX(C4:E4,1,Annahmen!$C$4)</f>
-        <v>36900</v>
+        <v>35793</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">Annahmen!$C$9*Annahmen!$C$11</f>
-        <v>7300</v>
+        <f aca="false">Annahmen!$C$9*Annahmen!$C$11*(1-Annahmen!$C$13)</f>
+        <v>6935</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">Annahmen!$D$9*Annahmen!$D$11</f>
-        <v>10220</v>
+        <f aca="false">Annahmen!$D$9*Annahmen!$D$11*(1-Annahmen!$D$13)</f>
+        <v>9913.4</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">Annahmen!$E$9*Annahmen!$E$11</f>
-        <v>13140</v>
+        <f aca="false">Annahmen!$E$9*Annahmen!$E$11*(1-Annahmen!$E$13)</f>
+        <v>12877.2</v>
       </c>
       <c r="F5" s="7" t="n">
         <f aca="false">INDEX(C5:E5,1,Annahmen!$C$4)</f>
-        <v>10220</v>
+        <v>9913.4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="32" t="n">
         <f aca="false">C4+C5</f>
-        <v>36000</v>
-      </c>
-      <c r="D6" s="33" t="n">
+        <v>34200</v>
+      </c>
+      <c r="D6" s="32" t="n">
         <f aca="false">D4+D5</f>
-        <v>47120</v>
-      </c>
-      <c r="E6" s="33" t="n">
+        <v>45706.4</v>
+      </c>
+      <c r="E6" s="32" t="n">
         <f aca="false">E4+E5</f>
-        <v>57215</v>
-      </c>
-      <c r="F6" s="33" t="n">
+        <v>56070.7</v>
+      </c>
+      <c r="F6" s="32" t="n">
         <f aca="false">INDEX(C6:E6,1,Annahmen!$C$4)</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>17</v>
@@ -4818,117 +5014,117 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="n">
-        <f aca="false">(Annahmen!$C$16*Annahmen!$C$14+(1-Annahmen!$C$16)*Annahmen!$C$15)*(1-Annahmen!$C$17)</f>
+      <c r="C8" s="24" t="n">
+        <f aca="false">(Annahmen!$C$17*Annahmen!$C$15+(1-Annahmen!$C$17)*Annahmen!$C$16)*(1-Annahmen!$C$18)</f>
         <v>25.6275</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <f aca="false">(Annahmen!$D$16*Annahmen!$D$14+(1-Annahmen!$D$16)*Annahmen!$D$15)*(1-Annahmen!$D$17)</f>
+      <c r="D8" s="24" t="n">
+        <f aca="false">(Annahmen!$D$17*Annahmen!$D$15+(1-Annahmen!$D$17)*Annahmen!$D$16)*(1-Annahmen!$D$18)</f>
         <v>28.776</v>
       </c>
-      <c r="E8" s="26" t="n">
-        <f aca="false">(Annahmen!$E$16*Annahmen!$E$14+(1-Annahmen!$E$16)*Annahmen!$E$15)*(1-Annahmen!$E$17)</f>
+      <c r="E8" s="24" t="n">
+        <f aca="false">(Annahmen!$E$17*Annahmen!$E$15+(1-Annahmen!$E$17)*Annahmen!$E$16)*(1-Annahmen!$E$18)</f>
         <v>31.725</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="24" t="n">
         <f aca="false">INDEX(C8:E8,1,Annahmen!$C$4)</f>
         <v>28.776</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="26" t="n">
-        <f aca="false">C8/(1+Annahmen!$C$18)</f>
+      <c r="C9" s="24" t="n">
+        <f aca="false">C8/(1+Annahmen!$C$19)</f>
         <v>22.679203539823</v>
       </c>
-      <c r="D9" s="26" t="n">
-        <f aca="false">D8/(1+Annahmen!$D$18)</f>
+      <c r="D9" s="24" t="n">
+        <f aca="false">D8/(1+Annahmen!$D$19)</f>
         <v>25.4654867256637</v>
       </c>
-      <c r="E9" s="26" t="n">
-        <f aca="false">E8/(1+Annahmen!$E$18)</f>
+      <c r="E9" s="24" t="n">
+        <f aca="false">E8/(1+Annahmen!$E$19)</f>
         <v>28.0752212389381</v>
       </c>
-      <c r="F9" s="26" t="n">
+      <c r="F9" s="24" t="n">
         <f aca="false">INDEX(C9:E9,1,Annahmen!$C$4)</f>
         <v>25.4654867256637</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C11" s="7" t="n">
         <f aca="false">C6*C9</f>
-        <v>816451.327433628</v>
+        <v>775628.761061947</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">D6*D9</f>
-        <v>1199933.73451327</v>
+        <v>1163935.72247788</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">E6*E9</f>
-        <v>1606323.78318584</v>
+        <v>1574197.30752212</v>
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">INDEX(C11:E11,1,Annahmen!$C$4)</f>
-        <v>1199933.73451327</v>
+        <v>1163935.72247788</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">C6*Annahmen!$C$20/(1+Annahmen!$C$21)</f>
-        <v>344347.826086957</v>
+        <f aca="false">C6*Annahmen!$C$21/(1+Annahmen!$C$22)</f>
+        <v>223043.47826087</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">D6*Annahmen!$D$20/(1+Annahmen!$D$21)</f>
-        <v>512173.913043478</v>
+        <f aca="false">D6*Annahmen!$D$21/(1+Annahmen!$D$22)</f>
+        <v>357702.260869565</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">E6*Annahmen!$E$20/(1+Annahmen!$E$21)</f>
-        <v>696530.434782609</v>
+        <f aca="false">E6*Annahmen!$E$21/(1+Annahmen!$E$22)</f>
+        <v>511949.869565217</v>
       </c>
       <c r="F12" s="7" t="n">
         <f aca="false">INDEX(C12:E12,1,Annahmen!$C$4)</f>
-        <v>512173.913043478</v>
+        <v>357702.260869565</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="4" t="n">
-        <f aca="false">Annahmen!$C$23</f>
+        <f aca="false">Annahmen!$C$24</f>
         <v>45000</v>
       </c>
       <c r="D13" s="4" t="n">
-        <f aca="false">Annahmen!$D$23</f>
+        <f aca="false">Annahmen!$D$24</f>
         <v>60000</v>
       </c>
       <c r="E13" s="4" t="n">
-        <f aca="false">Annahmen!$E$23</f>
+        <f aca="false">Annahmen!$E$24</f>
         <v>75000</v>
       </c>
       <c r="F13" s="7" t="n">
@@ -4938,21 +5134,21 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">Annahmen!$C$25*Annahmen!$C$26/(1+Annahmen!$C$27)*Annahmen!$C$28</f>
+        <f aca="false">Annahmen!$C$26*Annahmen!$C$27/(1+Annahmen!$C$28)*Annahmen!$C$29</f>
         <v>46875</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">Annahmen!$D$25*Annahmen!$D$26/(1+Annahmen!$D$27)*Annahmen!$D$28</f>
+        <f aca="false">Annahmen!$D$26*Annahmen!$D$27/(1+Annahmen!$D$28)*Annahmen!$D$29</f>
         <v>62500</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">Annahmen!$E$25*Annahmen!$E$26/(1+Annahmen!$E$27)*Annahmen!$E$28</f>
+        <f aca="false">Annahmen!$E$26*Annahmen!$E$27/(1+Annahmen!$E$28)*Annahmen!$E$29</f>
         <v>78125</v>
       </c>
       <c r="F14" s="7" t="n">
@@ -4962,21 +5158,21 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>300</v>
+        <v>314</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="7" t="n">
-        <f aca="false">Annahmen!$C$29*Annahmen!$C$30</f>
+        <f aca="false">Annahmen!$C$30*Annahmen!$C$31</f>
         <v>62500</v>
       </c>
       <c r="D15" s="7" t="n">
-        <f aca="false">Annahmen!$D$29*Annahmen!$D$30</f>
+        <f aca="false">Annahmen!$D$30*Annahmen!$D$31</f>
         <v>100000</v>
       </c>
       <c r="E15" s="7" t="n">
-        <f aca="false">Annahmen!$E$29*Annahmen!$E$30</f>
+        <f aca="false">Annahmen!$E$30*Annahmen!$E$31</f>
         <v>137500</v>
       </c>
       <c r="F15" s="7" t="n">
@@ -4986,26 +5182,26 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="33" t="n">
+      <c r="C16" s="32" t="n">
         <f aca="false">SUM(C11:C15)</f>
-        <v>1315174.15352059</v>
-      </c>
-      <c r="D16" s="33" t="n">
+        <v>1153047.23932282</v>
+      </c>
+      <c r="D16" s="32" t="n">
         <f aca="false">SUM(D11:D15)</f>
-        <v>1934607.64755675</v>
-      </c>
-      <c r="E16" s="33" t="n">
+        <v>1744137.98334744</v>
+      </c>
+      <c r="E16" s="32" t="n">
         <f aca="false">SUM(E11:E15)</f>
-        <v>2593479.21796845</v>
-      </c>
-      <c r="F16" s="33" t="n">
+        <v>2376772.17708734</v>
+      </c>
+      <c r="F16" s="32" t="n">
         <f aca="false">INDEX(C16:E16,1,Annahmen!$C$4)</f>
-        <v>1934607.64755675</v>
+        <v>1744137.98334744</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5015,21 +5211,21 @@
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="24" t="n">
         <f aca="false">C16/C6</f>
-        <v>36.5326153755718</v>
-      </c>
-      <c r="D17" s="26" t="n">
+        <v>33.7148315591467</v>
+      </c>
+      <c r="D17" s="24" t="n">
         <f aca="false">D16/D6</f>
-        <v>41.0570383607121</v>
-      </c>
-      <c r="E17" s="26" t="n">
+        <v>38.1596009168834</v>
+      </c>
+      <c r="E17" s="24" t="n">
         <f aca="false">E16/E6</f>
-        <v>45.3286588826086</v>
-      </c>
-      <c r="F17" s="26" t="n">
+        <v>42.3888443890899</v>
+      </c>
+      <c r="F17" s="24" t="n">
         <f aca="false">INDEX(C17:E17,1,Annahmen!$C$4)</f>
-        <v>41.0570383607121</v>
+        <v>38.1596009168834</v>
       </c>
     </row>
   </sheetData>
@@ -5048,7 +5244,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
@@ -5058,15 +5254,15 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -5083,45 +5279,45 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C4" s="7" t="n">
-        <f aca="false">Umsatz!C12*Annahmen!$C$22</f>
-        <v>110191.304347826</v>
+        <f aca="false">Umsatz!C12*Annahmen!$C$23</f>
+        <v>100369.565217391</v>
       </c>
       <c r="D4" s="7" t="n">
-        <f aca="false">Umsatz!D12*Annahmen!$D$22</f>
-        <v>163895.652173913</v>
+        <f aca="false">Umsatz!D12*Annahmen!$D$23</f>
+        <v>160966.017391304</v>
       </c>
       <c r="E4" s="7" t="n">
-        <f aca="false">Umsatz!E12*Annahmen!$E$22</f>
-        <v>222889.739130435</v>
+        <f aca="false">Umsatz!E12*Annahmen!$E$23</f>
+        <v>230377.441304348</v>
       </c>
       <c r="F4" s="7" t="n">
         <f aca="false">INDEX(C4:E4,1,Annahmen!$C$4)</f>
-        <v>163895.652173913</v>
+        <v>160966.017391304</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>306</v>
+        <v>320</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C5" s="7" t="n">
-        <f aca="false">Umsatz!C13*Annahmen!$C$24</f>
+        <f aca="false">Umsatz!C13*Annahmen!$C$25</f>
         <v>18000</v>
       </c>
       <c r="D5" s="7" t="n">
-        <f aca="false">Umsatz!D13*Annahmen!$D$24</f>
+        <f aca="false">Umsatz!D13*Annahmen!$D$25</f>
         <v>24000</v>
       </c>
       <c r="E5" s="7" t="n">
-        <f aca="false">Umsatz!E13*Annahmen!$E$24</f>
+        <f aca="false">Umsatz!E13*Annahmen!$E$25</f>
         <v>30000</v>
       </c>
       <c r="F5" s="7" t="n">
@@ -5131,45 +5327,45 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C6" s="7" t="n">
-        <f aca="false">Annahmen!$C$32*Annahmen!$C$33</f>
-        <v>1031513.805</v>
+        <f aca="false">Annahmen!$C$33*Annahmen!$C$34</f>
+        <v>444077.24768254</v>
       </c>
       <c r="D6" s="7" t="n">
-        <f aca="false">Annahmen!$D$32*Annahmen!$D$33</f>
-        <v>982394.1</v>
+        <f aca="false">Annahmen!$D$33*Annahmen!$D$34</f>
+        <v>383244.748</v>
       </c>
       <c r="E6" s="7" t="n">
-        <f aca="false">Annahmen!$E$32*Annahmen!$E$33</f>
-        <v>982394.1</v>
+        <f aca="false">Annahmen!$E$33*Annahmen!$E$34</f>
+        <v>425827.497777778</v>
       </c>
       <c r="F6" s="7" t="n">
         <f aca="false">INDEX(C6:E6,1,Annahmen!$C$4)</f>
-        <v>982394.1</v>
+        <v>383244.748</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>309</v>
+        <v>323</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C7" s="7" t="n">
-        <f aca="false">Annahmen!$C$34</f>
+        <f aca="false">Annahmen!$C$35</f>
         <v>220000</v>
       </c>
       <c r="D7" s="7" t="n">
-        <f aca="false">Annahmen!$D$34</f>
+        <f aca="false">Annahmen!$D$35</f>
         <v>180000</v>
       </c>
       <c r="E7" s="7" t="n">
-        <f aca="false">Annahmen!$E$34</f>
+        <f aca="false">Annahmen!$E$35</f>
         <v>160000</v>
       </c>
       <c r="F7" s="7" t="n">
@@ -5179,21 +5375,21 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>308</v>
+        <v>322</v>
       </c>
       <c r="C8" s="7" t="n">
-        <f aca="false">Annahmen!$C$35</f>
+        <f aca="false">Annahmen!$C$36</f>
         <v>40000</v>
       </c>
       <c r="D8" s="7" t="n">
-        <f aca="false">Annahmen!$D$35</f>
+        <f aca="false">Annahmen!$D$36</f>
         <v>40000</v>
       </c>
       <c r="E8" s="7" t="n">
-        <f aca="false">Annahmen!$E$35</f>
+        <f aca="false">Annahmen!$E$36</f>
         <v>40000</v>
       </c>
       <c r="F8" s="7" t="n">
@@ -5203,376 +5399,400 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C9" s="7" t="n">
-        <f aca="false">Umsatz!C6*Annahmen!$C$36</f>
-        <v>79200</v>
+        <f aca="false">Umsatz!C6*Annahmen!$C$37</f>
+        <v>75240</v>
       </c>
       <c r="D9" s="7" t="n">
-        <f aca="false">Umsatz!D6*Annahmen!$D$36</f>
-        <v>103664</v>
+        <f aca="false">Umsatz!D6*Annahmen!$D$37</f>
+        <v>100554.08</v>
       </c>
       <c r="E9" s="7" t="n">
-        <f aca="false">Umsatz!E6*Annahmen!$E$36</f>
-        <v>125873</v>
+        <f aca="false">Umsatz!E6*Annahmen!$E$37</f>
+        <v>123355.54</v>
       </c>
       <c r="F9" s="7" t="n">
         <f aca="false">INDEX(C9:E9,1,Annahmen!$C$4)</f>
-        <v>103664</v>
+        <v>100554.08</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="C10" s="7" t="n">
-        <f aca="false">Umsatz!C16*Annahmen!$C$37</f>
-        <v>52606.9661408234</v>
+        <f aca="false">Annahmen!$C$41+Annahmen!$C$42+Annahmen!$C$43+Annahmen!$C$44</f>
+        <v>165000</v>
       </c>
       <c r="D10" s="7" t="n">
-        <f aca="false">Umsatz!D16*Annahmen!$D$37</f>
-        <v>77384.3059022701</v>
+        <f aca="false">Annahmen!$D$41+Annahmen!$D$42+Annahmen!$D$43+Annahmen!$D$44</f>
+        <v>155000</v>
       </c>
       <c r="E10" s="7" t="n">
-        <f aca="false">Umsatz!E16*Annahmen!$E$37</f>
-        <v>103739.168718738</v>
+        <f aca="false">Annahmen!$E$41+Annahmen!$E$42+Annahmen!$E$43+Annahmen!$E$44</f>
+        <v>155000</v>
       </c>
       <c r="F10" s="7" t="n">
         <f aca="false">INDEX(C10:E10,1,Annahmen!$C$4)</f>
-        <v>77384.3059022701</v>
+        <v>155000</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="C11" s="7" t="n">
         <f aca="false">Umsatz!C16*Annahmen!$C$38</f>
-        <v>26303.4830704117</v>
+        <v>46121.8895729127</v>
       </c>
       <c r="D11" s="7" t="n">
         <f aca="false">Umsatz!D16*Annahmen!$D$38</f>
-        <v>38692.1529511351</v>
+        <v>69765.5193338977</v>
       </c>
       <c r="E11" s="7" t="n">
         <f aca="false">Umsatz!E16*Annahmen!$E$38</f>
-        <v>51869.584359369</v>
+        <v>95070.8870834937</v>
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">INDEX(C11:E11,1,Annahmen!$C$4)</f>
-        <v>38692.1529511351</v>
+        <v>69765.5193338977</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">Annahmen!$C$39</f>
-        <v>85000</v>
+        <f aca="false">Umsatz!C16*Annahmen!$C$39</f>
+        <v>23060.9447864563</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">Annahmen!$D$39</f>
-        <v>85000</v>
+        <f aca="false">Umsatz!D16*Annahmen!$D$39</f>
+        <v>34882.7596669488</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">Annahmen!$E$39</f>
-        <v>85000</v>
+        <f aca="false">Umsatz!E16*Annahmen!$E$39</f>
+        <v>47535.4435417468</v>
       </c>
       <c r="F12" s="7" t="n">
         <f aca="false">INDEX(C12:E12,1,Annahmen!$C$4)</f>
+        <v>34882.7596669488</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <f aca="false">Annahmen!$C$40</f>
         <v>85000</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="33" t="n">
-        <f aca="false">SUM(C4:C12)</f>
-        <v>1662815.55855906</v>
-      </c>
-      <c r="D13" s="33" t="n">
-        <f aca="false">SUM(D4:D12)</f>
-        <v>1695030.21102732</v>
-      </c>
-      <c r="E13" s="33" t="n">
-        <f aca="false">SUM(E4:E12)</f>
-        <v>1801765.59220854</v>
-      </c>
-      <c r="F13" s="33" t="n">
+      <c r="D13" s="7" t="n">
+        <f aca="false">Annahmen!$D$40</f>
+        <v>85000</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <f aca="false">Annahmen!$E$40</f>
+        <v>85000</v>
+      </c>
+      <c r="F13" s="7" t="n">
         <f aca="false">INDEX(C13:E13,1,Annahmen!$C$4)</f>
-        <v>1695030.21102732</v>
+        <v>85000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="B14" s="3"/>
-      <c r="C14" s="33" t="n">
-        <f aca="false">Umsatz!C16-C13</f>
-        <v>-347641.405038476</v>
-      </c>
-      <c r="D14" s="33" t="n">
-        <f aca="false">Umsatz!D16-D13</f>
-        <v>239577.436529435</v>
-      </c>
-      <c r="E14" s="33" t="n">
-        <f aca="false">Umsatz!E16-E13</f>
-        <v>791713.625759908</v>
-      </c>
-      <c r="F14" s="33" t="n">
+      <c r="C14" s="32" t="n">
+        <f aca="false">SUM(C4:C13)</f>
+        <v>1216869.6472593</v>
+      </c>
+      <c r="D14" s="32" t="n">
+        <f aca="false">SUM(D4:D13)</f>
+        <v>1233413.12439215</v>
+      </c>
+      <c r="E14" s="32" t="n">
+        <f aca="false">SUM(E4:E13)</f>
+        <v>1392166.80970737</v>
+      </c>
+      <c r="F14" s="32" t="n">
         <f aca="false">INDEX(C14:E14,1,Annahmen!$C$4)</f>
-        <v>239577.436529435</v>
+        <v>1233413.12439215</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>14</v>
+        <v>330</v>
       </c>
       <c r="B15" s="3"/>
-      <c r="C15" s="33" t="n">
-        <f aca="false">MAX(Annahmen!$C$42,Annahmen!$C$41*Umsatz!C16)</f>
-        <v>150000</v>
-      </c>
-      <c r="D15" s="33" t="n">
-        <f aca="false">MAX(Annahmen!$D$42,Annahmen!$D$41*Umsatz!D16)</f>
-        <v>193460.764755675</v>
-      </c>
-      <c r="E15" s="33" t="n">
-        <f aca="false">MAX(Annahmen!$E$42,Annahmen!$E$41*Umsatz!E16)</f>
-        <v>259347.921796845</v>
-      </c>
-      <c r="F15" s="33" t="n">
+      <c r="C15" s="32" t="n">
+        <f aca="false">Umsatz!C16-C14</f>
+        <v>-63822.4079364836</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <f aca="false">Umsatz!D16-D14</f>
+        <v>510724.858955291</v>
+      </c>
+      <c r="E15" s="32" t="n">
+        <f aca="false">Umsatz!E16-E14</f>
+        <v>984605.367379975</v>
+      </c>
+      <c r="F15" s="32" t="n">
         <f aca="false">INDEX(C15:E15,1,Annahmen!$C$4)</f>
-        <v>193460.764755675</v>
+        <v>510724.858955291</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>316</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3"/>
-      <c r="C16" s="33" t="n">
-        <f aca="false">C14-C15</f>
-        <v>-497641.405038476</v>
-      </c>
-      <c r="D16" s="33" t="n">
-        <f aca="false">D14-D15</f>
-        <v>46116.6717737592</v>
-      </c>
-      <c r="E16" s="33" t="n">
-        <f aca="false">E14-E15</f>
-        <v>532365.703963063</v>
-      </c>
-      <c r="F16" s="33" t="n">
+      <c r="C16" s="32" t="n">
+        <f aca="false">MAX(Annahmen!$C$47,Annahmen!$C$46*Umsatz!C16)</f>
+        <v>150000</v>
+      </c>
+      <c r="D16" s="32" t="n">
+        <f aca="false">MAX(Annahmen!$D$47,Annahmen!$D$46*Umsatz!D16)</f>
+        <v>174413.798334744</v>
+      </c>
+      <c r="E16" s="32" t="n">
+        <f aca="false">MAX(Annahmen!$E$47,Annahmen!$E$46*Umsatz!E16)</f>
+        <v>237677.217708734</v>
+      </c>
+      <c r="F16" s="32" t="n">
         <f aca="false">INDEX(C16:E16,1,Annahmen!$C$4)</f>
-        <v>46116.6717737592</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="9" t="n">
-        <f aca="false">C16/Umsatz!C16</f>
-        <v>-0.378384416775787</v>
-      </c>
-      <c r="D18" s="9" t="n">
-        <f aca="false">D16/Umsatz!D16</f>
-        <v>0.0238377387952543</v>
-      </c>
-      <c r="E18" s="9" t="n">
-        <f aca="false">E16/Umsatz!E16</f>
-        <v>0.205270857878738</v>
-      </c>
-      <c r="F18" s="9" t="n">
-        <f aca="false">INDEX(C18:E18,1,Annahmen!$C$4)</f>
-        <v>0.0238377387952543</v>
+        <v>174413.798334744</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="12" t="s">
+        <v>331</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="32" t="n">
+        <f aca="false">C15-C16</f>
+        <v>-213822.407936484</v>
+      </c>
+      <c r="D17" s="32" t="n">
+        <f aca="false">D15-D16</f>
+        <v>336311.060620546</v>
+      </c>
+      <c r="E17" s="32" t="n">
+        <f aca="false">E15-E16</f>
+        <v>746928.149671241</v>
+      </c>
+      <c r="F17" s="32" t="n">
+        <f aca="false">INDEX(C17:E17,1,Annahmen!$C$4)</f>
+        <v>336311.060620546</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>317</v>
+        <v>16</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C19" s="9" t="n">
-        <f aca="false">C6/Umsatz!C16</f>
-        <v>0.784317272536678</v>
+        <f aca="false">C17/Umsatz!C16</f>
+        <v>-0.185441151623641</v>
       </c>
       <c r="D19" s="9" t="n">
-        <f aca="false">D6/Umsatz!D16</f>
-        <v>0.507800173973612</v>
+        <f aca="false">D17/Umsatz!D16</f>
+        <v>0.192823654912371</v>
       </c>
       <c r="E19" s="9" t="n">
-        <f aca="false">E6/Umsatz!E16</f>
-        <v>0.378793897091467</v>
+        <f aca="false">E17/Umsatz!E16</f>
+        <v>0.314261567377727</v>
       </c>
       <c r="F19" s="9" t="n">
         <f aca="false">INDEX(C19:E19,1,Annahmen!$C$4)</f>
-        <v>0.507800173973612</v>
+        <v>0.192823654912371</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C20" s="9" t="n">
-        <f aca="false">C7/Umsatz!C16</f>
-        <v>0.167278226545954</v>
+        <f aca="false">C6/Umsatz!C16</f>
+        <v>0.385133611649203</v>
       </c>
       <c r="D20" s="9" t="n">
-        <f aca="false">D7/Umsatz!D16</f>
-        <v>0.0930421216039981</v>
+        <f aca="false">D6/Umsatz!D16</f>
+        <v>0.219733043864142</v>
       </c>
       <c r="E20" s="9" t="n">
-        <f aca="false">E7/Umsatz!E16</f>
-        <v>0.0616931876266712</v>
+        <f aca="false">E6/Umsatz!E16</f>
+        <v>0.179162101392324</v>
       </c>
       <c r="F20" s="9" t="n">
         <f aca="false">INDEX(C20:E20,1,Annahmen!$C$4)</f>
-        <v>0.0930421216039981</v>
+        <v>0.219733043864142</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="C21" s="9" t="n">
-        <f aca="false">C15/Umsatz!C16</f>
-        <v>0.114053336281332</v>
+        <f aca="false">C7/Umsatz!C16</f>
+        <v>0.190798774323597</v>
       </c>
       <c r="D21" s="9" t="n">
-        <f aca="false">D15/Umsatz!D16</f>
-        <v>0.1</v>
+        <f aca="false">D7/Umsatz!D16</f>
+        <v>0.103202843879665</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">E15/Umsatz!E16</f>
-        <v>0.1</v>
+        <f aca="false">E7/Umsatz!E16</f>
+        <v>0.0673181895776291</v>
       </c>
       <c r="F21" s="9" t="n">
         <f aca="false">INDEX(C21:E21,1,Annahmen!$C$4)</f>
-        <v>0.1</v>
+        <v>0.103202843879665</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="7" t="n">
-        <f aca="false">C6+C7+C8+C12</f>
-        <v>1376513.805</v>
-      </c>
-      <c r="D22" s="7" t="n">
-        <f aca="false">D6+D7+D8+D12</f>
-        <v>1287394.1</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <f aca="false">E6+E7+E8+E12</f>
-        <v>1267394.1</v>
-      </c>
-      <c r="F22" s="7" t="n">
+        <v>334</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <f aca="false">C16/Umsatz!C16</f>
+        <v>0.130090073402452</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <f aca="false">D16/Umsatz!D16</f>
+        <v>0.1</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <f aca="false">E16/Umsatz!E16</f>
+        <v>0.1</v>
+      </c>
+      <c r="F22" s="9" t="n">
         <f aca="false">INDEX(C22:E22,1,Annahmen!$C$4)</f>
-        <v>1287394.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="26" t="n">
-        <f aca="false">(Umsatz!C16*(1-Annahmen!$C$41)-C4-C5-C9-C10-C11)/Umsatz!C6</f>
-        <v>24.9265273502629</v>
-      </c>
-      <c r="D23" s="26" t="n">
-        <f aca="false">(Umsatz!D16*(1-Annahmen!$D$41)-D4-D5-D9-D10-D11)/Umsatz!D6</f>
-        <v>28.3003134926519</v>
-      </c>
-      <c r="E23" s="26" t="n">
-        <f aca="false">(Umsatz!E16*(1-Annahmen!$E$41)-E4-E5-E9-E10-E11)/Umsatz!E6</f>
-        <v>31.4560832642325</v>
-      </c>
-      <c r="F23" s="26" t="n">
+        <v>335</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="7" t="n">
+        <f aca="false">C6+C10+C7+C8+C13</f>
+        <v>954077.24768254</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <f aca="false">D6+D10+D7+D8+D13</f>
+        <v>843244.748</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <f aca="false">E6+E10+E7+E8+E13</f>
+        <v>865827.497777778</v>
+      </c>
+      <c r="F23" s="7" t="n">
         <f aca="false">INDEX(C23:E23,1,Annahmen!$C$4)</f>
-        <v>28.3003134926519</v>
+        <v>843244.748</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="3" t="s">
-        <v>322</v>
+        <v>336</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <f aca="false">C22/C23</f>
-        <v>55222.8469556743</v>
-      </c>
-      <c r="D24" s="7" t="n">
-        <f aca="false">D22/D23</f>
-        <v>45490.4536776339</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <f aca="false">E22/E23</f>
-        <v>40290.9061930512</v>
-      </c>
-      <c r="F24" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="C24" s="24" t="n">
+        <f aca="false">(Umsatz!C16*(1-Annahmen!$C$46)-C4-C5-C9-C11-C12)/Umsatz!C6</f>
+        <v>22.6593601115139</v>
+      </c>
+      <c r="D24" s="24" t="n">
+        <f aca="false">(Umsatz!D16*(1-Annahmen!$D$46)-D4-D5-D9-D11-D12)/Umsatz!D6</f>
+        <v>25.8072350616226</v>
+      </c>
+      <c r="E24" s="24" t="n">
+        <f aca="false">(Umsatz!E16*(1-Annahmen!$E$46)-E4-E5-E9-E11-E12)/Umsatz!E6</f>
+        <v>28.7628948354313</v>
+      </c>
+      <c r="F24" s="24" t="n">
         <f aca="false">INDEX(C24:E24,1,Annahmen!$C$4)</f>
-        <v>45490.4536776339</v>
+        <v>25.8072350616226</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>323</v>
+        <v>337</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <f aca="false">C23/C24</f>
+        <v>42105.215813122</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <f aca="false">D23/D24</f>
+        <v>32674.7420243392</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <f aca="false">E23/E24</f>
+        <v>30102.2377174364</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <f aca="false">INDEX(C25:E25,1,Annahmen!$C$4)</f>
+        <v>32674.7420243392</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C25" s="9" t="n">
-        <f aca="false">C24/Umsatz!C6</f>
-        <v>1.53396797099095</v>
-      </c>
-      <c r="D25" s="9" t="n">
-        <f aca="false">D24/Umsatz!D6</f>
-        <v>0.965417098421772</v>
-      </c>
-      <c r="E25" s="9" t="n">
-        <f aca="false">E24/Umsatz!E6</f>
-        <v>0.704201803601349</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <f aca="false">INDEX(C25:E25,1,Annahmen!$C$4)</f>
-        <v>0.965417098421772</v>
+      <c r="C26" s="9" t="n">
+        <f aca="false">C25/Umsatz!C6</f>
+        <v>1.2311466612024</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <f aca="false">D25/Umsatz!D6</f>
+        <v>0.714883299151524</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <f aca="false">E25/Umsatz!E6</f>
+        <v>0.536862170749365</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <f aca="false">INDEX(C26:E26,1,Annahmen!$C$4)</f>
+        <v>0.714883299151524</v>
       </c>
     </row>
   </sheetData>
@@ -5591,633 +5811,600 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="B2" s="35"/>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
+      <c r="A2" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B4" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>31</v>
+        <v>206</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B5" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>328</v>
+        <v>343</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <f aca="false">B7-B4</f>
+        <v>145</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="B6" s="4" t="n">
+        <v>345</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="B7" s="4" t="n">
         <f aca="false">Annahmen!$D$8+Annahmen!$D$9</f>
         <v>351</v>
       </c>
-      <c r="J6" s="18" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <f aca="false">(B4+B5)*B6</f>
-        <v>4563</v>
-      </c>
-      <c r="J7" s="18"/>
+      <c r="K7" s="18" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B8" s="16" t="n">
-        <v>40</v>
-      </c>
-      <c r="J8" s="18" t="s">
-        <v>333</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <f aca="false">B4*12+B5*8+B6*B7</f>
+        <v>3983</v>
+      </c>
+      <c r="K8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B9" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>335</v>
+        <v>2</v>
+      </c>
+      <c r="K9" s="18" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B10" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="J10" s="18" t="s">
-        <v>337</v>
+        <v>6</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>31</v>
+        <v>354</v>
+      </c>
+      <c r="B11" s="7" t="n">
+        <f aca="false">B8*B9+B4*B10</f>
+        <v>9202</v>
+      </c>
+      <c r="K11" s="18" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B12" s="7" t="n">
-        <f aca="false">B8*52-B9*B8-(B10+B11)*B8/5</f>
-        <v>1696</v>
-      </c>
-      <c r="J12" s="18" t="s">
-        <v>340</v>
+        <v>356</v>
+      </c>
+      <c r="B12" s="16" t="n">
+        <v>40</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="B13" s="26" t="n">
-        <f aca="false">B7/B12</f>
-        <v>2.69044811320755</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>342</v>
+        <v>358</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="K13" s="18" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B14" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="J14" s="18" t="s">
-        <v>344</v>
+        <v>13</v>
+      </c>
+      <c r="K14" s="18" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B15" s="20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>346</v>
+        <v>362</v>
+      </c>
+      <c r="B15" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" s="18" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B16" s="20" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J16" s="18" t="s">
-        <v>348</v>
+        <v>363</v>
+      </c>
+      <c r="B16" s="7" t="n">
+        <f aca="false">B12*52-B13*B12-(B14+B15)*B12/5</f>
+        <v>1696</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B17" s="16" t="n">
-        <v>30000</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>358</v>
+        <v>365</v>
+      </c>
+      <c r="B17" s="24" t="n">
+        <f aca="false">B8/B16</f>
+        <v>2.34846698113208</v>
+      </c>
+      <c r="K17" s="18"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="B18" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="K18" s="18" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B19" s="20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K19" s="18" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="16" t="n">
-        <v>4300</v>
-      </c>
-      <c r="E20" s="7" t="n">
-        <f aca="false">C20*D20*$B$14</f>
-        <v>60200</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <f aca="false">E20*$B$15</f>
-        <v>3612</v>
-      </c>
-      <c r="G20" s="7" t="n">
-        <f aca="false">(E20+F20)*$B$16</f>
-        <v>18505.48</v>
-      </c>
-      <c r="H20" s="7" t="n">
-        <f aca="false">E20+F20+G20</f>
-        <v>82317.48</v>
-      </c>
-      <c r="I20" s="26" t="n">
-        <f aca="false">C20*$B$12/$B$7</f>
-        <v>0.371685294762218</v>
-      </c>
-      <c r="J20" s="18" t="s">
-        <v>361</v>
+        <v>370</v>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="16" t="n">
-        <v>3200</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <f aca="false">C21*D21*$B$14</f>
-        <v>44800</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <f aca="false">E21*$B$15</f>
-        <v>2688</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <f aca="false">(E21+F21)*$B$16</f>
-        <v>13771.52</v>
-      </c>
-      <c r="H21" s="7" t="n">
-        <f aca="false">E21+F21+G21</f>
-        <v>61259.52</v>
-      </c>
-      <c r="I21" s="26" t="n">
-        <f aca="false">C21*$B$12/$B$7</f>
-        <v>0.371685294762218</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>363</v>
+        <v>372</v>
+      </c>
+      <c r="B21" s="16" t="n">
+        <v>40000</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="16" t="n">
-        <v>3100</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <f aca="false">C22*D22*$B$14</f>
-        <v>43400</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <f aca="false">E22*$B$15</f>
-        <v>2604</v>
-      </c>
-      <c r="G22" s="7" t="n">
-        <f aca="false">(E22+F22)*$B$16</f>
-        <v>13341.16</v>
-      </c>
-      <c r="H22" s="7" t="n">
-        <f aca="false">E22+F22+G22</f>
-        <v>59345.16</v>
-      </c>
-      <c r="I22" s="26" t="n">
-        <f aca="false">C22*$B$12/$B$7</f>
-        <v>0.371685294762218</v>
-      </c>
-      <c r="J22" s="18" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" s="16" t="n">
-        <v>2850</v>
-      </c>
-      <c r="E23" s="7" t="n">
-        <f aca="false">C23*D23*$B$14</f>
-        <v>39900</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <f aca="false">E23*$B$15</f>
-        <v>2394</v>
-      </c>
-      <c r="G23" s="7" t="n">
-        <f aca="false">(E23+F23)*$B$16</f>
-        <v>12265.26</v>
-      </c>
-      <c r="H23" s="7" t="n">
-        <f aca="false">E23+F23+G23</f>
-        <v>54559.26</v>
-      </c>
-      <c r="I23" s="26" t="n">
-        <f aca="false">C23*$B$12/$B$7</f>
-        <v>0.371685294762218</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D24" s="16" t="n">
-        <v>2500</v>
-      </c>
-      <c r="E24" s="7" t="n">
-        <f aca="false">C24*D24*$B$14</f>
-        <v>140000</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <f aca="false">E24*$B$15</f>
-        <v>8400</v>
-      </c>
-      <c r="G24" s="7" t="n">
-        <f aca="false">(E24+F24)*$B$16</f>
-        <v>43036</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <f aca="false">E24+F24+G24</f>
-        <v>191436</v>
-      </c>
-      <c r="I24" s="26" t="n">
-        <f aca="false">C24*$B$12/$B$7</f>
-        <v>1.48674117904887</v>
-      </c>
-      <c r="J24" s="18" t="s">
-        <v>371</v>
+        <v>374</v>
+      </c>
+      <c r="B22" s="16" t="n">
+        <v>982000</v>
+      </c>
+      <c r="K22" s="18" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="3" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="C25" s="36" t="n">
-        <v>4</v>
+        <v>386</v>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D25" s="16" t="n">
-        <v>2200</v>
+        <v>4300</v>
       </c>
       <c r="E25" s="7" t="n">
-        <f aca="false">C25*D25*$B$14</f>
-        <v>123200</v>
+        <f aca="false">C25*D25*$B$18</f>
+        <v>60200</v>
       </c>
       <c r="F25" s="7" t="n">
-        <f aca="false">E25*$B$15</f>
-        <v>7392</v>
+        <f aca="false">E25*$B$19</f>
+        <v>3612</v>
       </c>
       <c r="G25" s="7" t="n">
-        <f aca="false">(E25+F25)*$B$16</f>
-        <v>37871.68</v>
+        <f aca="false">(E25+F25)*$B$20</f>
+        <v>18505.48</v>
       </c>
       <c r="H25" s="7" t="n">
         <f aca="false">E25+F25+G25</f>
-        <v>168463.68</v>
-      </c>
-      <c r="I25" s="26" t="n">
-        <f aca="false">C25*$B$12/$B$7</f>
-        <v>1.48674117904887</v>
-      </c>
-      <c r="J25" s="18" t="s">
-        <v>374</v>
+        <v>82317.48</v>
+      </c>
+      <c r="I25" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J25" s="7" t="n">
+        <f aca="false">C25*$B$16*I25</f>
+        <v>848</v>
+      </c>
+      <c r="K25" s="18" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>3</v>
+        <v>386</v>
+      </c>
+      <c r="C26" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D26" s="16" t="n">
-        <v>2050</v>
+        <v>2950</v>
       </c>
       <c r="E26" s="7" t="n">
-        <f aca="false">C26*D26*$B$14</f>
-        <v>86100</v>
+        <f aca="false">C26*D26*$B$18</f>
+        <v>41300</v>
       </c>
       <c r="F26" s="7" t="n">
-        <f aca="false">E26*$B$15</f>
-        <v>5166</v>
+        <f aca="false">E26*$B$19</f>
+        <v>2478</v>
       </c>
       <c r="G26" s="7" t="n">
-        <f aca="false">(E26+F26)*$B$16</f>
-        <v>26467.14</v>
+        <f aca="false">(E26+F26)*$B$20</f>
+        <v>12695.62</v>
       </c>
       <c r="H26" s="7" t="n">
         <f aca="false">E26+F26+G26</f>
-        <v>117733.14</v>
-      </c>
-      <c r="I26" s="26" t="n">
-        <f aca="false">C26*$B$12/$B$7</f>
-        <v>1.11505588428665</v>
-      </c>
-      <c r="J26" s="18" t="s">
-        <v>377</v>
+        <v>56473.62</v>
+      </c>
+      <c r="I26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" s="7" t="n">
+        <f aca="false">C26*$B$16*I26</f>
+        <v>1696</v>
+      </c>
+      <c r="K26" s="18" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="3" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>2</v>
+        <v>391</v>
+      </c>
+      <c r="C27" s="35" t="n">
+        <v>3</v>
       </c>
       <c r="D27" s="16" t="n">
-        <v>2450</v>
+        <v>2500</v>
       </c>
       <c r="E27" s="7" t="n">
-        <f aca="false">C27*D27*$B$14</f>
-        <v>68600</v>
+        <f aca="false">C27*D27*$B$18</f>
+        <v>105000</v>
       </c>
       <c r="F27" s="7" t="n">
-        <f aca="false">E27*$B$15</f>
-        <v>4116</v>
+        <f aca="false">E27*$B$19</f>
+        <v>6300</v>
       </c>
       <c r="G27" s="7" t="n">
-        <f aca="false">(E27+F27)*$B$16</f>
-        <v>21087.64</v>
+        <f aca="false">(E27+F27)*$B$20</f>
+        <v>32277</v>
       </c>
       <c r="H27" s="7" t="n">
         <f aca="false">E27+F27+G27</f>
-        <v>93803.64</v>
-      </c>
-      <c r="I27" s="26" t="n">
-        <f aca="false">C27*$B$12/$B$7</f>
-        <v>0.743370589524436</v>
-      </c>
-      <c r="J27" s="18" t="s">
-        <v>185</v>
+        <v>143577</v>
+      </c>
+      <c r="I27" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" s="7" t="n">
+        <f aca="false">C27*$B$16*I27</f>
+        <v>5088</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>392</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="3" t="s">
-        <v>380</v>
+        <v>393</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>3</v>
+        <v>394</v>
+      </c>
+      <c r="C28" s="35" t="n">
+        <v>1</v>
       </c>
       <c r="D28" s="16" t="n">
-        <v>2150</v>
+        <v>2250</v>
       </c>
       <c r="E28" s="7" t="n">
-        <f aca="false">C28*D28*$B$14</f>
-        <v>90300</v>
+        <f aca="false">C28*D28*$B$18</f>
+        <v>31500</v>
       </c>
       <c r="F28" s="7" t="n">
-        <f aca="false">E28*$B$15</f>
-        <v>5418</v>
+        <f aca="false">E28*$B$19</f>
+        <v>1890</v>
       </c>
       <c r="G28" s="7" t="n">
-        <f aca="false">(E28+F28)*$B$16</f>
-        <v>27758.22</v>
+        <f aca="false">(E28+F28)*$B$20</f>
+        <v>9683.1</v>
       </c>
       <c r="H28" s="7" t="n">
         <f aca="false">E28+F28+G28</f>
-        <v>123476.22</v>
-      </c>
-      <c r="I28" s="26" t="n">
-        <f aca="false">C28*$B$12/$B$7</f>
-        <v>1.11505588428665</v>
-      </c>
-      <c r="J28" s="18" t="s">
-        <v>381</v>
+        <v>43073.1</v>
+      </c>
+      <c r="I28" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="7" t="n">
+        <f aca="false">C28*$B$16*I28</f>
+        <v>1696</v>
+      </c>
+      <c r="K28" s="18" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="12" t="s">
-        <v>382</v>
-      </c>
-      <c r="C29" s="37" t="n">
-        <f aca="false">SUM(C20:C28)</f>
-        <v>20</v>
-      </c>
-      <c r="E29" s="33" t="n">
-        <f aca="false">SUM(E20:E28)</f>
-        <v>696500</v>
-      </c>
-      <c r="F29" s="33" t="n">
-        <f aca="false">SUM(F20:F28)</f>
-        <v>41790</v>
-      </c>
-      <c r="G29" s="33" t="n">
-        <f aca="false">SUM(G20:G28)</f>
-        <v>214104.1</v>
-      </c>
-      <c r="H29" s="33" t="n">
-        <f aca="false">SUM(H20:H28)</f>
-        <v>952394.1</v>
-      </c>
-      <c r="I29" s="38" t="n">
-        <f aca="false">SUM(I20:I28)</f>
-        <v>7.43370589524436</v>
+      <c r="A29" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D29" s="16" t="n">
+        <v>3100</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <f aca="false">C29*D29*$B$18</f>
+        <v>13020</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <f aca="false">E29*$B$19</f>
+        <v>781.2</v>
+      </c>
+      <c r="G29" s="7" t="n">
+        <f aca="false">(E29+F29)*$B$20</f>
+        <v>4002.348</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <f aca="false">E29+F29+G29</f>
+        <v>17803.548</v>
+      </c>
+      <c r="I29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="7" t="n">
+        <f aca="false">C29*$B$16*I29</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="18" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <f aca="false">B17</f>
-        <v>30000</v>
+      <c r="A30" s="12" t="s">
+        <v>399</v>
+      </c>
+      <c r="C30" s="36" t="n">
+        <f aca="false">SUM(C25:C29)</f>
+        <v>6.3</v>
+      </c>
+      <c r="E30" s="32" t="n">
+        <f aca="false">SUM(E25:E29)</f>
+        <v>251020</v>
+      </c>
+      <c r="F30" s="32" t="n">
+        <f aca="false">SUM(F25:F29)</f>
+        <v>15061.2</v>
+      </c>
+      <c r="G30" s="32" t="n">
+        <f aca="false">SUM(G25:G29)</f>
+        <v>77163.548</v>
+      </c>
+      <c r="H30" s="32" t="n">
+        <f aca="false">SUM(H25:H29)</f>
+        <v>343244.748</v>
+      </c>
+      <c r="J30" s="32" t="n">
+        <f aca="false">SUM(J25:J29)</f>
+        <v>9328</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="H31" s="34" t="n">
-        <f aca="false">H29+H30</f>
-        <v>982394.1</v>
+      <c r="A31" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <f aca="false">B21</f>
+        <v>40000</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="H32" s="7" t="n">
-        <f aca="false">H31/C29</f>
-        <v>49119.705</v>
+      <c r="A32" s="12" t="s">
+        <v>401</v>
+      </c>
+      <c r="H32" s="33" t="n">
+        <f aca="false">H30+H31</f>
+        <v>383244.748</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <f aca="false">H31/Umsatz!F16</f>
-        <v>0.507800173973612</v>
+        <v>402</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <f aca="false">H32/C30</f>
+        <v>60832.4996825397</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <f aca="false">H32/Umsatz!F16</f>
+        <v>0.219733043864142</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
-        <v>387</v>
+      <c r="A35" s="12" t="s">
+        <v>404</v>
+      </c>
+      <c r="H35" s="21" t="n">
+        <f aca="false">J30/B11</f>
+        <v>1.01369267550532</v>
+      </c>
+      <c r="I35" s="12" t="str">
+        <f aca="false">IF(H35&gt;=1,"OK","UNTERDECKUNG")</f>
+        <v>OK</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <f aca="false">B22-H32</f>
+        <v>598755.252</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <f aca="false">-Betriebskosten!D10</f>
+        <v>-155000</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="s">
+        <v>407</v>
+      </c>
+      <c r="H38" s="32" t="n">
+        <f aca="false">H36+H37</f>
+        <v>443755.252</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A2:K2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6243,7 +6430,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6257,91 +6444,91 @@
         <v>11</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="B5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+0,"0")</f>
+        <v>420</v>
+      </c>
+      <c r="B5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+0,"0")</f>
         <v>2029</v>
       </c>
-      <c r="C5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+1,"0")</f>
+      <c r="C5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+1,"0")</f>
         <v>2030</v>
       </c>
-      <c r="D5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+2,"0")</f>
+      <c r="D5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+2,"0")</f>
         <v>2031</v>
       </c>
-      <c r="E5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+3,"0")</f>
+      <c r="E5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+3,"0")</f>
         <v>2032</v>
       </c>
-      <c r="F5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+4,"0")</f>
+      <c r="F5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+4,"0")</f>
         <v>2033</v>
       </c>
-      <c r="G5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+5,"0")</f>
+      <c r="G5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+5,"0")</f>
         <v>2034</v>
       </c>
-      <c r="H5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+6,"0")</f>
+      <c r="H5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+6,"0")</f>
         <v>2035</v>
       </c>
-      <c r="I5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+7,"0")</f>
+      <c r="I5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+7,"0")</f>
         <v>2036</v>
       </c>
-      <c r="J5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+8,"0")</f>
+      <c r="J5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+8,"0")</f>
         <v>2037</v>
       </c>
-      <c r="K5" s="39" t="str">
-        <f aca="false">TEXT(Annahmen!$F$50+9,"0")</f>
+      <c r="K5" s="37" t="str">
+        <f aca="false">TEXT(Annahmen!$F$55+9,"0")</f>
         <v>2038</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="B6" s="9" t="n">
-        <f aca="false">Annahmen!$F$51</f>
+        <f aca="false">Annahmen!$F$56</f>
         <v>0.75</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">Annahmen!$F$52</f>
+        <f aca="false">Annahmen!$F$57</f>
         <v>0.9</v>
       </c>
       <c r="D6" s="9" t="n">
@@ -6379,91 +6566,91 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="B7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^0</f>
+        <v>422</v>
+      </c>
+      <c r="B7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^0</f>
         <v>1</v>
       </c>
-      <c r="C7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^1</f>
+      <c r="C7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^1</f>
         <v>1.025</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^2</f>
+      <c r="D7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^2</f>
         <v>1.050625</v>
       </c>
-      <c r="E7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^3</f>
+      <c r="E7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^3</f>
         <v>1.076890625</v>
       </c>
-      <c r="F7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^4</f>
+      <c r="F7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^4</f>
         <v>1.103812890625</v>
       </c>
-      <c r="G7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^5</f>
+      <c r="G7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^5</f>
         <v>1.13140821289062</v>
       </c>
-      <c r="H7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^6</f>
+      <c r="H7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^6</f>
         <v>1.15969341821289</v>
       </c>
-      <c r="I7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^7</f>
+      <c r="I7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^7</f>
         <v>1.18868575366821</v>
       </c>
-      <c r="J7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^8</f>
+      <c r="J7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^8</f>
         <v>1.21840289750992</v>
       </c>
-      <c r="K7" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$53)^9</f>
+      <c r="K7" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$58)^9</f>
         <v>1.24886296994767</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^0</f>
+        <v>423</v>
+      </c>
+      <c r="B8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^0</f>
         <v>1</v>
       </c>
-      <c r="C8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^1</f>
+      <c r="C8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^1</f>
         <v>1.03</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^2</f>
+      <c r="D8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^2</f>
         <v>1.0609</v>
       </c>
-      <c r="E8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^3</f>
+      <c r="E8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^3</f>
         <v>1.092727</v>
       </c>
-      <c r="F8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^4</f>
+      <c r="F8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^4</f>
         <v>1.12550881</v>
       </c>
-      <c r="G8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^5</f>
+      <c r="G8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^5</f>
         <v>1.1592740743</v>
       </c>
-      <c r="H8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^6</f>
+      <c r="H8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^6</f>
         <v>1.194052296529</v>
       </c>
-      <c r="I8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^7</f>
+      <c r="I8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^7</f>
         <v>1.22987386542487</v>
       </c>
-      <c r="J8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^8</f>
+      <c r="J8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^8</f>
         <v>1.26677008138762</v>
       </c>
-      <c r="K8" s="26" t="n">
-        <f aca="false">(1+Annahmen!$F$54)^9</f>
+      <c r="K8" s="24" t="n">
+        <f aca="false">(1+Annahmen!$F$59)^9</f>
         <v>1.30477318382925</v>
       </c>
     </row>
@@ -6473,368 +6660,368 @@
       </c>
       <c r="B9" s="7" t="n">
         <f aca="false">Umsatz!F6*B6</f>
-        <v>35340</v>
+        <v>34279.8</v>
       </c>
       <c r="C9" s="7" t="n">
         <f aca="false">Umsatz!F6*C6</f>
-        <v>42408</v>
+        <v>41135.76</v>
       </c>
       <c r="D9" s="7" t="n">
         <f aca="false">Umsatz!F6*D6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="E9" s="7" t="n">
         <f aca="false">Umsatz!F6*E6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="F9" s="7" t="n">
         <f aca="false">Umsatz!F6*F6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="G9" s="7" t="n">
         <f aca="false">Umsatz!F6*G6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="H9" s="7" t="n">
         <f aca="false">Umsatz!F6*H6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="I9" s="7" t="n">
         <f aca="false">Umsatz!F6*I6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="J9" s="7" t="n">
         <f aca="false">Umsatz!F6*J6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
       <c r="K9" s="7" t="n">
         <f aca="false">Umsatz!F6*K6</f>
-        <v>47120</v>
+        <v>45706.4</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="33" t="n">
+      <c r="B10" s="32" t="n">
         <f aca="false">Umsatz!F16*B6*B7</f>
-        <v>1450955.73566756</v>
-      </c>
-      <c r="C10" s="33" t="n">
+        <v>1308103.48751058</v>
+      </c>
+      <c r="C10" s="32" t="n">
         <f aca="false">Umsatz!F16*C6*C7</f>
-        <v>1784675.5548711</v>
-      </c>
-      <c r="D10" s="33" t="n">
+        <v>1608967.28963801</v>
+      </c>
+      <c r="D10" s="32" t="n">
         <f aca="false">Umsatz!F16*D6*D7</f>
-        <v>2032547.15971431</v>
-      </c>
-      <c r="E10" s="33" t="n">
+        <v>1832434.96875441</v>
+      </c>
+      <c r="E10" s="32" t="n">
         <f aca="false">Umsatz!F16*E6*E7</f>
-        <v>2083360.83870717</v>
-      </c>
-      <c r="F10" s="33" t="n">
+        <v>1878245.84297327</v>
+      </c>
+      <c r="F10" s="32" t="n">
         <f aca="false">Umsatz!F16*F6*F7</f>
-        <v>2135444.85967485</v>
-      </c>
-      <c r="G10" s="33" t="n">
+        <v>1925201.9890476</v>
+      </c>
+      <c r="G10" s="32" t="n">
         <f aca="false">Umsatz!F16*G6*G7</f>
-        <v>2188830.98116672</v>
-      </c>
-      <c r="H10" s="33" t="n">
+        <v>1973332.03877379</v>
+      </c>
+      <c r="H10" s="32" t="n">
         <f aca="false">Umsatz!F16*H6*H7</f>
-        <v>2243551.75569589</v>
-      </c>
-      <c r="I10" s="33" t="n">
+        <v>2022665.33974313</v>
+      </c>
+      <c r="I10" s="32" t="n">
         <f aca="false">Umsatz!F16*I6*I7</f>
-        <v>2299640.54958829</v>
-      </c>
-      <c r="J10" s="33" t="n">
+        <v>2073231.97323671</v>
+      </c>
+      <c r="J10" s="32" t="n">
         <f aca="false">Umsatz!F16*J6*J7</f>
-        <v>2357131.56332799</v>
-      </c>
-      <c r="K10" s="33" t="n">
+        <v>2125062.77256763</v>
+      </c>
+      <c r="K10" s="32" t="n">
         <f aca="false">Umsatz!F16*K6*K7</f>
-        <v>2416059.85241119</v>
+        <v>2178189.34188182</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="B11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*B6*B8</f>
-        <v>305727.083270489</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*B6*B8</f>
+        <v>292626.282294113</v>
       </c>
       <c r="C11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*C6*C8</f>
-        <v>377878.674922324</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*C6*C8</f>
+        <v>361686.084915524</v>
       </c>
       <c r="D11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*D6*D8</f>
-        <v>432461.150188882</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*D6*D8</f>
+        <v>413929.630514433</v>
       </c>
       <c r="E11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*E6*E8</f>
-        <v>445434.984694548</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*E6*E8</f>
+        <v>426347.519429866</v>
       </c>
       <c r="F11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*F6*F8</f>
-        <v>458798.034235385</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*F6*F8</f>
+        <v>439137.945012762</v>
       </c>
       <c r="G11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*G6*G8</f>
-        <v>472561.975262446</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*G6*G8</f>
+        <v>452312.083363145</v>
       </c>
       <c r="H11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*H6*H8</f>
-        <v>486738.83452032</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*H6*H8</f>
+        <v>465881.445864039</v>
       </c>
       <c r="I11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*I6*I8</f>
-        <v>501340.99955593</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*I6*I8</f>
+        <v>479857.88923996</v>
       </c>
       <c r="J11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*J6*J8</f>
-        <v>516381.229542607</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*J6*J8</f>
+        <v>494253.625917159</v>
       </c>
       <c r="K11" s="7" t="n">
-        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F10+Betriebskosten!F11)*K6*K8</f>
-        <v>531872.666428886</v>
+        <f aca="false">(Betriebskosten!F4+Betriebskosten!F5+Betriebskosten!F9+Betriebskosten!F11+Betriebskosten!F12)*K6*K8</f>
+        <v>509081.234694674</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="B12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*B8</f>
-        <v>1287394.1</v>
+        <f aca="false">Betriebskosten!F23*B8</f>
+        <v>843244.748</v>
       </c>
       <c r="C12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*C8</f>
-        <v>1326015.923</v>
+        <f aca="false">Betriebskosten!F23*C8</f>
+        <v>868542.09044</v>
       </c>
       <c r="D12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*D8</f>
-        <v>1365796.40069</v>
+        <f aca="false">Betriebskosten!F23*D8</f>
+        <v>894598.3531532</v>
       </c>
       <c r="E12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*E8</f>
-        <v>1406770.2927107</v>
+        <f aca="false">Betriebskosten!F23*E8</f>
+        <v>921436.303747796</v>
       </c>
       <c r="F12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*F8</f>
-        <v>1448973.40149202</v>
+        <f aca="false">Betriebskosten!F23*F8</f>
+        <v>949079.39286023</v>
       </c>
       <c r="G12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*G8</f>
-        <v>1492442.60353678</v>
+        <f aca="false">Betriebskosten!F23*G8</f>
+        <v>977551.774646037</v>
       </c>
       <c r="H12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*H8</f>
-        <v>1537215.88164289</v>
+        <f aca="false">Betriebskosten!F23*H8</f>
+        <v>1006878.32788542</v>
       </c>
       <c r="I12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*I8</f>
-        <v>1583332.35809217</v>
+        <f aca="false">Betriebskosten!F23*I8</f>
+        <v>1037084.67772198</v>
       </c>
       <c r="J12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*J8</f>
-        <v>1630832.32883494</v>
+        <f aca="false">Betriebskosten!F23*J8</f>
+        <v>1068197.21805364</v>
       </c>
       <c r="K12" s="7" t="n">
-        <f aca="false">Betriebskosten!F22*K8</f>
-        <v>1679757.29869999</v>
+        <f aca="false">Betriebskosten!F23*K8</f>
+        <v>1100243.13459525</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="B13" s="7" t="n">
         <f aca="false">B10-B11-B12</f>
-        <v>-142165.447602924</v>
+        <v>172232.457216468</v>
       </c>
       <c r="C13" s="7" t="n">
         <f aca="false">C10-C11-C12</f>
-        <v>80780.9569487802</v>
+        <v>378739.114282491</v>
       </c>
       <c r="D13" s="7" t="n">
         <f aca="false">D10-D11-D12</f>
-        <v>234289.608835432</v>
+        <v>523906.985086773</v>
       </c>
       <c r="E13" s="7" t="n">
         <f aca="false">E10-E11-E12</f>
-        <v>231155.561301922</v>
+        <v>530462.019795603</v>
       </c>
       <c r="F13" s="7" t="n">
         <f aca="false">F10-F11-F12</f>
-        <v>227673.423947443</v>
+        <v>536984.651174605</v>
       </c>
       <c r="G13" s="7" t="n">
         <f aca="false">G10-G11-G12</f>
-        <v>223826.402367493</v>
+        <v>543468.180764605</v>
       </c>
       <c r="H13" s="7" t="n">
         <f aca="false">H10-H11-H12</f>
-        <v>219597.039532684</v>
+        <v>549905.565993674</v>
       </c>
       <c r="I13" s="7" t="n">
         <f aca="false">I10-I11-I12</f>
-        <v>214967.191940184</v>
+        <v>556289.406274768</v>
       </c>
       <c r="J13" s="7" t="n">
         <f aca="false">J10-J11-J12</f>
-        <v>209918.004950448</v>
+        <v>562611.928596827</v>
       </c>
       <c r="K13" s="7" t="n">
         <f aca="false">K10-K11-K12</f>
-        <v>204429.887282321</v>
+        <v>568864.972591894</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="B14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*B8,Annahmen!$F$41*B10)</f>
+        <f aca="false">MAX(Annahmen!$F$47*B8,Annahmen!$F$46*B10)</f>
         <v>150000</v>
       </c>
       <c r="C14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*C8,Annahmen!$F$41*C10)</f>
-        <v>178467.55548711</v>
+        <f aca="false">MAX(Annahmen!$F$47*C8,Annahmen!$F$46*C10)</f>
+        <v>160896.728963802</v>
       </c>
       <c r="D14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*D8,Annahmen!$F$41*D10)</f>
-        <v>203254.715971431</v>
+        <f aca="false">MAX(Annahmen!$F$47*D8,Annahmen!$F$46*D10)</f>
+        <v>183243.496875441</v>
       </c>
       <c r="E14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*E8,Annahmen!$F$41*E10)</f>
-        <v>208336.083870717</v>
+        <f aca="false">MAX(Annahmen!$F$47*E8,Annahmen!$F$46*E10)</f>
+        <v>187824.584297327</v>
       </c>
       <c r="F14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*F8,Annahmen!$F$41*F10)</f>
-        <v>213544.485967485</v>
+        <f aca="false">MAX(Annahmen!$F$47*F8,Annahmen!$F$46*F10)</f>
+        <v>192520.19890476</v>
       </c>
       <c r="G14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*G8,Annahmen!$F$41*G10)</f>
-        <v>218883.098116672</v>
+        <f aca="false">MAX(Annahmen!$F$47*G8,Annahmen!$F$46*G10)</f>
+        <v>197333.203877379</v>
       </c>
       <c r="H14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*H8,Annahmen!$F$41*H10)</f>
-        <v>224355.175569589</v>
+        <f aca="false">MAX(Annahmen!$F$47*H8,Annahmen!$F$46*H10)</f>
+        <v>202266.533974313</v>
       </c>
       <c r="I14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*I8,Annahmen!$F$41*I10)</f>
-        <v>229964.054958829</v>
+        <f aca="false">MAX(Annahmen!$F$47*I8,Annahmen!$F$46*I10)</f>
+        <v>207323.197323671</v>
       </c>
       <c r="J14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*J8,Annahmen!$F$41*J10)</f>
-        <v>235713.156332799</v>
+        <f aca="false">MAX(Annahmen!$F$47*J8,Annahmen!$F$46*J10)</f>
+        <v>212506.277256763</v>
       </c>
       <c r="K14" s="7" t="n">
-        <f aca="false">MAX(Annahmen!$F$42*K8,Annahmen!$F$41*K10)</f>
-        <v>241605.985241119</v>
+        <f aca="false">MAX(Annahmen!$F$47*K8,Annahmen!$F$46*K10)</f>
+        <v>217818.934188182</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="33" t="n">
+      <c r="B15" s="32" t="n">
         <f aca="false">B13-B14</f>
-        <v>-292165.447602924</v>
-      </c>
-      <c r="C15" s="33" t="n">
+        <v>22232.4572164678</v>
+      </c>
+      <c r="C15" s="32" t="n">
         <f aca="false">C13-C14</f>
-        <v>-97686.5985383302</v>
-      </c>
-      <c r="D15" s="33" t="n">
+        <v>217842.385318689</v>
+      </c>
+      <c r="D15" s="32" t="n">
         <f aca="false">D13-D14</f>
-        <v>31034.8928640002</v>
-      </c>
-      <c r="E15" s="33" t="n">
+        <v>340663.488211332</v>
+      </c>
+      <c r="E15" s="32" t="n">
         <f aca="false">E13-E14</f>
-        <v>22819.4774312051</v>
-      </c>
-      <c r="F15" s="33" t="n">
+        <v>342637.435498277</v>
+      </c>
+      <c r="F15" s="32" t="n">
         <f aca="false">F13-F14</f>
-        <v>14128.9379799583</v>
-      </c>
-      <c r="G15" s="33" t="n">
+        <v>344464.452269845</v>
+      </c>
+      <c r="G15" s="32" t="n">
         <f aca="false">G13-G14</f>
-        <v>4943.30425082057</v>
-      </c>
-      <c r="H15" s="33" t="n">
+        <v>346134.976887226</v>
+      </c>
+      <c r="H15" s="32" t="n">
         <f aca="false">H13-H14</f>
-        <v>-4758.13603690534</v>
-      </c>
-      <c r="I15" s="33" t="n">
+        <v>347639.032019361</v>
+      </c>
+      <c r="I15" s="32" t="n">
         <f aca="false">I13-I14</f>
-        <v>-14996.8630186444</v>
-      </c>
-      <c r="J15" s="33" t="n">
+        <v>348966.208951097</v>
+      </c>
+      <c r="J15" s="32" t="n">
         <f aca="false">J13-J14</f>
-        <v>-25795.1513823515</v>
-      </c>
-      <c r="K15" s="33" t="n">
+        <v>350105.651340065</v>
+      </c>
+      <c r="K15" s="32" t="n">
         <f aca="false">K13-K14</f>
-        <v>-37176.097958798</v>
+        <v>351046.038403712</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="B16" s="7" t="n">
         <f aca="false">B15</f>
-        <v>-292165.447602924</v>
+        <v>22232.4572164678</v>
       </c>
       <c r="C16" s="7" t="n">
         <f aca="false">B16+C15</f>
-        <v>-389852.046141254</v>
+        <v>240074.842535157</v>
       </c>
       <c r="D16" s="7" t="n">
         <f aca="false">C16+D15</f>
-        <v>-358817.153277254</v>
+        <v>580738.330746489</v>
       </c>
       <c r="E16" s="7" t="n">
         <f aca="false">D16+E15</f>
-        <v>-335997.675846049</v>
+        <v>923375.766244766</v>
       </c>
       <c r="F16" s="7" t="n">
         <f aca="false">E16+F15</f>
-        <v>-321868.737866091</v>
+        <v>1267840.21851461</v>
       </c>
       <c r="G16" s="7" t="n">
         <f aca="false">F16+G15</f>
-        <v>-316925.43361527</v>
+        <v>1613975.19540184</v>
       </c>
       <c r="H16" s="7" t="n">
         <f aca="false">G16+H15</f>
-        <v>-321683.569652176</v>
+        <v>1961614.2274212</v>
       </c>
       <c r="I16" s="7" t="n">
         <f aca="false">H16+I15</f>
-        <v>-336680.43267082</v>
+        <v>2310580.4363723</v>
       </c>
       <c r="J16" s="7" t="n">
         <f aca="false">I16+J15</f>
-        <v>-362475.584053172</v>
+        <v>2660686.08771236</v>
       </c>
       <c r="K16" s="7" t="n">
         <f aca="false">J16+K15</f>
-        <v>-399651.68201197</v>
+        <v>3011732.12611607</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="B18" s="7" t="n">
         <f aca="false">B14</f>
@@ -6842,282 +7029,282 @@
       </c>
       <c r="C18" s="7" t="n">
         <f aca="false">C14</f>
-        <v>178467.55548711</v>
+        <v>160896.728963802</v>
       </c>
       <c r="D18" s="7" t="n">
         <f aca="false">D14</f>
-        <v>203254.715971431</v>
+        <v>183243.496875441</v>
       </c>
       <c r="E18" s="7" t="n">
         <f aca="false">E14</f>
-        <v>208336.083870717</v>
+        <v>187824.584297327</v>
       </c>
       <c r="F18" s="7" t="n">
         <f aca="false">F14</f>
-        <v>213544.485967485</v>
+        <v>192520.19890476</v>
       </c>
       <c r="G18" s="7" t="n">
         <f aca="false">G14</f>
-        <v>218883.098116672</v>
+        <v>197333.203877379</v>
       </c>
       <c r="H18" s="7" t="n">
         <f aca="false">H14</f>
-        <v>224355.175569589</v>
+        <v>202266.533974313</v>
       </c>
       <c r="I18" s="7" t="n">
         <f aca="false">I14</f>
-        <v>229964.054958829</v>
+        <v>207323.197323671</v>
       </c>
       <c r="J18" s="7" t="n">
         <f aca="false">J14</f>
-        <v>235713.156332799</v>
+        <v>212506.277256763</v>
       </c>
       <c r="K18" s="7" t="n">
         <f aca="false">K14</f>
-        <v>241605.985241119</v>
+        <v>217818.934188182</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="3" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="B19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*B8</f>
-        <v>-54904</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*B8</f>
+        <v>-55024</v>
       </c>
       <c r="C19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*C8</f>
-        <v>-56551.12</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*C8</f>
+        <v>-56674.72</v>
       </c>
       <c r="D19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*D8</f>
-        <v>-58247.6536</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*D8</f>
+        <v>-58374.9616</v>
       </c>
       <c r="E19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*E8</f>
-        <v>-59995.083208</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*E8</f>
+        <v>-60126.210448</v>
       </c>
       <c r="F19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*F8</f>
-        <v>-61794.93570424</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*F8</f>
+        <v>-61929.99676144</v>
       </c>
       <c r="G19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*G8</f>
-        <v>-63648.7837753672</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*G8</f>
+        <v>-63787.8966642832</v>
       </c>
       <c r="H19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*H8</f>
-        <v>-65558.2472886282</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*H8</f>
+        <v>-65701.5335642117</v>
       </c>
       <c r="I19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*I8</f>
-        <v>-67524.9947072871</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*I8</f>
+        <v>-67672.5795711381</v>
       </c>
       <c r="J19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*J8</f>
-        <v>-69550.7445485057</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*J8</f>
+        <v>-69702.7569582722</v>
       </c>
       <c r="K19" s="7" t="n">
-        <f aca="false">-Investition!$F$49*Annahmen!$F$45*K8</f>
-        <v>-71637.2668849609</v>
+        <f aca="false">-Investition!$F$49*Annahmen!$F$50*K8</f>
+        <v>-71793.8396670204</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="3" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="B20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*B8</f>
+        <f aca="false">-Annahmen!$F$51*B8</f>
         <v>-25000</v>
       </c>
       <c r="C20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*C8</f>
+        <f aca="false">-Annahmen!$F$51*C8</f>
         <v>-25750</v>
       </c>
       <c r="D20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*D8</f>
+        <f aca="false">-Annahmen!$F$51*D8</f>
         <v>-26522.5</v>
       </c>
       <c r="E20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*E8</f>
+        <f aca="false">-Annahmen!$F$51*E8</f>
         <v>-27318.175</v>
       </c>
       <c r="F20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*F8</f>
+        <f aca="false">-Annahmen!$F$51*F8</f>
         <v>-28137.72025</v>
       </c>
       <c r="G20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*G8</f>
+        <f aca="false">-Annahmen!$F$51*G8</f>
         <v>-28981.8518575</v>
       </c>
       <c r="H20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*H8</f>
+        <f aca="false">-Annahmen!$F$51*H8</f>
         <v>-29851.307413225</v>
       </c>
       <c r="I20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*I8</f>
+        <f aca="false">-Annahmen!$F$51*I8</f>
         <v>-30746.8466356218</v>
       </c>
       <c r="J20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*J8</f>
+        <f aca="false">-Annahmen!$F$51*J8</f>
         <v>-31669.2520346904</v>
       </c>
       <c r="K20" s="7" t="n">
-        <f aca="false">-Annahmen!$F$46*K8</f>
+        <f aca="false">-Annahmen!$F$51*K8</f>
         <v>-32619.3295957311</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="B21" s="33" t="n">
+        <v>431</v>
+      </c>
+      <c r="B21" s="32" t="n">
         <f aca="false">SUM(B18:B20)</f>
-        <v>70096</v>
-      </c>
-      <c r="C21" s="33" t="n">
+        <v>69976</v>
+      </c>
+      <c r="C21" s="32" t="n">
         <f aca="false">SUM(C18:C20)</f>
-        <v>96166.4354871105</v>
-      </c>
-      <c r="D21" s="33" t="n">
+        <v>78472.0089638015</v>
+      </c>
+      <c r="D21" s="32" t="n">
         <f aca="false">SUM(D18:D20)</f>
-        <v>118484.562371431</v>
-      </c>
-      <c r="E21" s="33" t="n">
+        <v>98346.0352754406</v>
+      </c>
+      <c r="E21" s="32" t="n">
         <f aca="false">SUM(E18:E20)</f>
-        <v>121022.825662717</v>
-      </c>
-      <c r="F21" s="33" t="n">
+        <v>100380.198849327</v>
+      </c>
+      <c r="F21" s="32" t="n">
         <f aca="false">SUM(F18:F20)</f>
-        <v>123611.830013245</v>
-      </c>
-      <c r="G21" s="33" t="n">
+        <v>102452.48189332</v>
+      </c>
+      <c r="G21" s="32" t="n">
         <f aca="false">SUM(G18:G20)</f>
-        <v>126252.462483805</v>
-      </c>
-      <c r="H21" s="33" t="n">
+        <v>104563.455355595</v>
+      </c>
+      <c r="H21" s="32" t="n">
         <f aca="false">SUM(H18:H20)</f>
-        <v>128945.620867736</v>
-      </c>
-      <c r="I21" s="33" t="n">
+        <v>106713.692996876</v>
+      </c>
+      <c r="I21" s="32" t="n">
         <f aca="false">SUM(I18:I20)</f>
-        <v>131692.21361592</v>
-      </c>
-      <c r="J21" s="33" t="n">
+        <v>108903.771116911</v>
+      </c>
+      <c r="J21" s="32" t="n">
         <f aca="false">SUM(J18:J20)</f>
-        <v>134493.159749603</v>
-      </c>
-      <c r="K21" s="33" t="n">
+        <v>111134.2682638</v>
+      </c>
+      <c r="K21" s="32" t="n">
         <f aca="false">SUM(K18:K20)</f>
-        <v>137349.388760427</v>
+        <v>113405.76492543</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="3" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="B22" s="7" t="n">
         <f aca="false">B21</f>
-        <v>70096</v>
+        <v>69976</v>
       </c>
       <c r="C22" s="7" t="n">
         <f aca="false">B22+C21</f>
-        <v>166262.43548711</v>
+        <v>148448.008963802</v>
       </c>
       <c r="D22" s="7" t="n">
         <f aca="false">C22+D21</f>
-        <v>284746.997858542</v>
+        <v>246794.044239242</v>
       </c>
       <c r="E22" s="7" t="n">
         <f aca="false">D22+E21</f>
-        <v>405769.823521259</v>
+        <v>347174.243088569</v>
       </c>
       <c r="F22" s="7" t="n">
         <f aca="false">E22+F21</f>
-        <v>529381.653534504</v>
+        <v>449626.724981888</v>
       </c>
       <c r="G22" s="7" t="n">
         <f aca="false">F22+G21</f>
-        <v>655634.116018309</v>
+        <v>554190.180337484</v>
       </c>
       <c r="H22" s="7" t="n">
         <f aca="false">G22+H21</f>
-        <v>784579.736886045</v>
+        <v>660903.87333436</v>
       </c>
       <c r="I22" s="7" t="n">
         <f aca="false">H22+I21</f>
-        <v>916271.950501964</v>
+        <v>769807.644451271</v>
       </c>
       <c r="J22" s="7" t="n">
         <f aca="false">I22+J21</f>
-        <v>1050765.11025157</v>
+        <v>880941.912715071</v>
       </c>
       <c r="K22" s="7" t="n">
         <f aca="false">J22+K21</f>
-        <v>1188114.49901199</v>
+        <v>994347.677640502</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="B23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*B8</f>
-        <v>22398.58548</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*B8</f>
+        <v>8737.9802544</v>
       </c>
       <c r="C23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*C8</f>
-        <v>23070.5430444</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*C8</f>
+        <v>9000.119662032</v>
       </c>
       <c r="D23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*D8</f>
-        <v>23762.659335732</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*D8</f>
+        <v>9270.12325189296</v>
       </c>
       <c r="E23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*E8</f>
-        <v>24475.539115804</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*E8</f>
+        <v>9548.22694944975</v>
       </c>
       <c r="F23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*F8</f>
-        <v>25209.8052892781</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*F8</f>
+        <v>9834.67375793324</v>
       </c>
       <c r="G23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*G8</f>
-        <v>25966.0994479564</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*G8</f>
+        <v>10129.7139706712</v>
       </c>
       <c r="H23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*H8</f>
-        <v>26745.0824313951</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*H8</f>
+        <v>10433.6053897914</v>
       </c>
       <c r="I23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*I8</f>
-        <v>27547.434904337</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*I8</f>
+        <v>10746.6135514851</v>
       </c>
       <c r="J23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*J8</f>
-        <v>28373.8579514671</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*J8</f>
+        <v>11069.0119580297</v>
       </c>
       <c r="K23" s="7" t="n">
-        <f aca="false">Betriebskosten!F6*Annahmen!$F$48*Annahmen!$F$47*K8</f>
-        <v>29225.0736900111</v>
+        <f aca="false">Betriebskosten!F6*Annahmen!$F$53*Annahmen!$F$52*K8</f>
+        <v>11401.0823167706</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="B25" s="17" t="n">
         <f aca="false">SUM(B21:K21)</f>
-        <v>1188114.49901199</v>
+        <v>994347.677640502</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="B26" s="9" t="n">
         <f aca="false">B25/Investition!$F$58</f>
-        <v>0.138843436602483</v>
+        <v>0.1164155387097</v>
       </c>
     </row>
   </sheetData>
@@ -7151,89 +7338,89 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="40" t="s">
-        <v>416</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="A2" s="38" t="s">
+        <v>437</v>
+      </c>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="D4" s="4" t="n">
         <f aca="false">Investition!$F$58</f>
-        <v>8557224.8</v>
+        <v>8541365.6</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="D5" s="29" t="n">
+        <v>439</v>
+      </c>
+      <c r="D5" s="28" t="n">
         <v>0.1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="D6" s="29" t="n">
+        <v>441</v>
+      </c>
+      <c r="D6" s="28" t="n">
         <v>0.15</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="D7" s="29" t="n">
+        <v>443</v>
+      </c>
+      <c r="D7" s="28" t="n">
         <v>0.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="3" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="B10" s="19" t="n">
         <v>5700</v>
@@ -7241,27 +7428,27 @@
       <c r="C10" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="D10" s="41"/>
+      <c r="D10" s="39"/>
       <c r="E10" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B10/$B$17+(1-$D$7)*C10/$C$17)+IF(D10="x",$D$6,0)</f>
         <v>0.184313933729822</v>
       </c>
       <c r="F10" s="7" t="n">
         <f aca="false">$D$4*E10</f>
-        <v>1577215.76469839</v>
+        <v>1574292.69316058</v>
       </c>
       <c r="G10" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E10/(1-$D$5)</f>
-        <v>24331.7841149263</v>
+        <v>20363.5702178926</v>
       </c>
       <c r="H10" s="7" t="n">
         <f aca="false">F10/B10</f>
-        <v>276.704520122524</v>
+        <v>276.191700554487</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="3" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="B11" s="19" t="n">
         <v>3500</v>
@@ -7269,27 +7456,27 @@
       <c r="C11" s="19" t="n">
         <v>45000</v>
       </c>
-      <c r="D11" s="41"/>
+      <c r="D11" s="39"/>
       <c r="E11" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B11/$B$17+(1-$D$7)*C11/$C$17)+IF(D11="x",$D$6,0)</f>
         <v>0.112457519116398</v>
       </c>
       <c r="F11" s="7" t="n">
         <f aca="false">$D$4*E11</f>
-        <v>962324.271529312</v>
+        <v>960540.785242141</v>
       </c>
       <c r="G11" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E11/(1-$D$5)</f>
-        <v>14845.8232205678</v>
+        <v>12424.6525518447</v>
       </c>
       <c r="H11" s="7" t="n">
         <f aca="false">F11/B11</f>
-        <v>274.949791865518</v>
+        <v>274.440224354897</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="B12" s="19" t="n">
         <v>1650</v>
@@ -7297,8 +7484,8 @@
       <c r="C12" s="19" t="n">
         <v>120000</v>
       </c>
-      <c r="D12" s="41" t="s">
-        <v>434</v>
+      <c r="D12" s="39" t="s">
+        <v>455</v>
       </c>
       <c r="E12" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B12/$B$17+(1-$D$7)*C12/$C$17)+IF(D12="x",$D$6,0)</f>
@@ -7306,20 +7493,20 @@
       </c>
       <c r="F12" s="7" t="n">
         <f aca="false">$D$4*E12</f>
-        <v>2313613.30669499</v>
+        <v>2309325.46139337</v>
       </c>
       <c r="G12" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E12/(1-$D$5)</f>
-        <v>35692.224718974</v>
+        <v>29871.2630715707</v>
       </c>
       <c r="H12" s="7" t="n">
         <f aca="false">F12/B12</f>
-        <v>1402.18988284545</v>
+        <v>1399.59118872326</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="3" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="B13" s="19" t="n">
         <v>1600</v>
@@ -7327,27 +7514,27 @@
       <c r="C13" s="19" t="n">
         <v>100000</v>
       </c>
-      <c r="D13" s="41"/>
+      <c r="D13" s="39"/>
       <c r="E13" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B13/$B$17+(1-$D$7)*C13/$C$17)+IF(D13="x",$D$6,0)</f>
         <v>0.105564995751912</v>
       </c>
       <c r="F13" s="7" t="n">
         <f aca="false">$D$4*E13</f>
-        <v>903343.399660153</v>
+        <v>901669.223279524</v>
       </c>
       <c r="G13" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E13/(1-$D$5)</f>
-        <v>13935.9224489984</v>
+        <v>11663.1453740048</v>
       </c>
       <c r="H13" s="7" t="n">
         <f aca="false">F13/B13</f>
-        <v>564.589624787596</v>
+        <v>563.543264549703</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="3" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="B14" s="19" t="n">
         <v>1550</v>
@@ -7355,27 +7542,27 @@
       <c r="C14" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="D14" s="41"/>
+      <c r="D14" s="39"/>
       <c r="E14" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B14/$B$17+(1-$D$7)*C14/$C$17)+IF(D14="x",$D$6,0)</f>
         <v>0.0873513169073917</v>
       </c>
       <c r="F14" s="7" t="n">
         <f aca="false">$D$4*E14</f>
-        <v>747484.855352591</v>
+        <v>746099.533347494</v>
       </c>
       <c r="G14" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E14/(1-$D$5)</f>
-        <v>11531.4851250515</v>
+        <v>9650.84212285604</v>
       </c>
       <c r="H14" s="7" t="n">
         <f aca="false">F14/B14</f>
-        <v>482.248293775865</v>
+        <v>481.354537643544</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="B15" s="19" t="n">
         <v>1200</v>
@@ -7383,27 +7570,27 @@
       <c r="C15" s="19" t="n">
         <v>70000</v>
       </c>
-      <c r="D15" s="41"/>
+      <c r="D15" s="39"/>
       <c r="E15" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B15/$B$17+(1-$D$7)*C15/$C$17)+IF(D15="x",$D$6,0)</f>
         <v>0.0757646559048428</v>
       </c>
       <c r="F15" s="7" t="n">
         <f aca="false">$D$4*E15</f>
-        <v>648335.192472388</v>
+        <v>647133.625641461</v>
       </c>
       <c r="G15" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E15/(1-$D$5)</f>
-        <v>10001.8984659109</v>
+        <v>8370.71218291246</v>
       </c>
       <c r="H15" s="7" t="n">
         <f aca="false">F15/B15</f>
-        <v>540.279327060323</v>
+        <v>539.278021367884</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="3" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="B16" s="19" t="n">
         <v>850</v>
@@ -7411,56 +7598,56 @@
       <c r="C16" s="19" t="n">
         <v>65000</v>
       </c>
-      <c r="D16" s="41"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="9" t="n">
         <f aca="false">(1-$D$5-$D$6)*($D$7*B16/$B$17+(1-$D$7)*C16/$C$17)+IF(D16="x",$D$6,0)</f>
         <v>0.064177994902294</v>
       </c>
       <c r="F16" s="7" t="n">
         <f aca="false">$D$4*E16</f>
-        <v>549185.529592184</v>
+        <v>548167.717935429</v>
       </c>
       <c r="G16" s="7" t="n">
         <f aca="false">AVERAGE(GuV_10J!$B$21:$K$21)*E16/(1-$D$5)</f>
-        <v>8472.31180677037</v>
+        <v>7090.58224296888</v>
       </c>
       <c r="H16" s="7" t="n">
         <f aca="false">F16/B16</f>
-        <v>646.100623049628</v>
+        <v>644.903197571093</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>439</v>
-      </c>
-      <c r="B17" s="33" t="n">
+        <v>460</v>
+      </c>
+      <c r="B17" s="32" t="n">
         <f aca="false">SUM(B10:B16)</f>
         <v>16050</v>
       </c>
-      <c r="C17" s="33" t="n">
+      <c r="C17" s="32" t="n">
         <f aca="false">SUM(C10:C16)</f>
         <v>550000</v>
       </c>
-      <c r="E17" s="42" t="n">
+      <c r="E17" s="40" t="n">
         <f aca="false">SUM(E10:E16)</f>
         <v>0.9</v>
       </c>
-      <c r="F17" s="33" t="n">
+      <c r="F17" s="32" t="n">
         <f aca="false">SUM(F10:F16)</f>
-        <v>7701502.32</v>
-      </c>
-      <c r="G17" s="33" t="n">
+        <v>7687229.04</v>
+      </c>
+      <c r="G17" s="32" t="n">
         <f aca="false">SUM(G10:G16)</f>
-        <v>118811.449901199</v>
-      </c>
-      <c r="H17" s="33" t="n">
+        <v>99434.7677640502</v>
+      </c>
+      <c r="H17" s="32" t="n">
         <f aca="false">F17/B17</f>
-        <v>479.844381308411</v>
+        <v>478.955080373832</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">D5</f>
@@ -7468,12 +7655,12 @@
       </c>
       <c r="F18" s="7" t="n">
         <f aca="false">$D$4*E18</f>
-        <v>855722.48</v>
+        <v>854136.56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="E19" s="21" t="n">
         <f aca="false">E17+E18</f>
@@ -7481,7 +7668,7 @@
       </c>
       <c r="F19" s="17" t="n">
         <f aca="false">F17+F18</f>
-        <v>8557224.8</v>
+        <v>8541365.6</v>
       </c>
       <c r="G19" s="12" t="str">
         <f aca="false">IF(ABS(F19-D4)&lt;1,"OK","FEHLER")</f>
@@ -7490,7 +7677,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="18" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
     </row>
   </sheetData>
